--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10575</v>
+        <v>0.119</v>
       </c>
       <c r="E2">
-        <v>0.1845</v>
+        <v>0.07875</v>
       </c>
       <c r="F2">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G2">
-        <v>0.03770543113213171</v>
+        <v>0.05156349083873344</v>
       </c>
       <c r="H2">
-        <v>0.02228549852802153</v>
+        <v>0.03505864360431767</v>
       </c>
       <c r="I2">
-        <v>0.0257373056616072</v>
+        <v>0.03352328218460806</v>
       </c>
       <c r="J2">
-        <v>0.02148741436327975</v>
+        <v>0.02780904834564419</v>
       </c>
       <c r="K2">
-        <v>887.4309999999999</v>
+        <v>849.735</v>
       </c>
       <c r="L2">
-        <v>0.3149178701309024</v>
+        <v>0.367313036633395</v>
       </c>
       <c r="M2">
-        <v>485.573</v>
+        <v>415.121</v>
       </c>
       <c r="N2">
-        <v>0.0447575372620764</v>
+        <v>0.04928236117881338</v>
       </c>
       <c r="O2">
-        <v>0.5471670473535407</v>
+        <v>0.4885299534560775</v>
       </c>
       <c r="P2">
-        <v>448.339</v>
+        <v>355.622</v>
       </c>
       <c r="Q2">
-        <v>0.0413255051218706</v>
+        <v>0.04221875512713637</v>
       </c>
       <c r="R2">
-        <v>0.5052099825225849</v>
+        <v>0.4185092999582223</v>
       </c>
       <c r="S2">
-        <v>37.23399999999999</v>
+        <v>59.49899999999999</v>
       </c>
       <c r="T2">
-        <v>0.07668054031010783</v>
+        <v>0.1433292943503219</v>
       </c>
       <c r="U2">
-        <v>1837.322</v>
+        <v>2237.605</v>
       </c>
       <c r="V2">
-        <v>0.169354572592448</v>
+        <v>0.2656441321578979</v>
       </c>
       <c r="W2">
-        <v>0.3368376367686162</v>
+        <v>0.1694444444444445</v>
       </c>
       <c r="X2">
-        <v>0.03712971927108098</v>
+        <v>0.07141096375083038</v>
       </c>
       <c r="Y2">
-        <v>0.2997079174975352</v>
+        <v>0.09803348069361408</v>
       </c>
       <c r="Z2">
-        <v>2.695579308320725</v>
+        <v>1.722281335698823</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03634768134156449</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="AC2">
-        <v>-0.0365535478747899</v>
+        <v>-0.07027919394934221</v>
       </c>
       <c r="AD2">
-        <v>359.199</v>
+        <v>540.989</v>
       </c>
       <c r="AE2">
-        <v>0.009451704633910202</v>
+        <v>0.009379682446117919</v>
       </c>
       <c r="AF2">
-        <v>359.2084517046339</v>
+        <v>540.9983796824461</v>
       </c>
       <c r="AG2">
-        <v>-1478.113548295366</v>
+        <v>-1696.606620317554</v>
       </c>
       <c r="AH2">
-        <v>0.03204879200019968</v>
+        <v>0.06035021040852762</v>
       </c>
       <c r="AI2">
-        <v>0.1049026239993694</v>
+        <v>0.1275113042935009</v>
       </c>
       <c r="AJ2">
-        <v>-0.1577352280289596</v>
+        <v>-0.2522193274773218</v>
       </c>
       <c r="AK2">
-        <v>-0.9314551439440268</v>
+        <v>-0.8461273330918835</v>
       </c>
       <c r="AL2">
-        <v>1.978</v>
+        <v>3.5</v>
       </c>
       <c r="AM2">
-        <v>-3.209000000000001</v>
+        <v>-1.961</v>
       </c>
       <c r="AN2">
-        <v>4.772647551221068</v>
+        <v>6.742472206989381</v>
       </c>
       <c r="AO2">
-        <v>36.66279069767442</v>
+        <v>22.15542857142857</v>
       </c>
       <c r="AP2">
-        <v>-19.63957306868494</v>
+        <v>-21.14520440098651</v>
       </c>
       <c r="AQ2">
-        <v>-22.59862885634154</v>
+        <v>-39.54309026007139</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRP Advisory Group plc (AIM:FRP)</t>
+          <t>Argentex Group PLC (AIM:AGFX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,44 +724,41 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.04</v>
-      </c>
       <c r="G3">
-        <v>0.2014987510407993</v>
+        <v>0.3196116504854369</v>
       </c>
       <c r="H3">
-        <v>0.2014987510407993</v>
+        <v>0.2893203883495146</v>
       </c>
       <c r="I3">
-        <v>0.1756869275603664</v>
+        <v>0.2893203883495146</v>
       </c>
       <c r="J3">
-        <v>0.1409739066076177</v>
+        <v>0.221956238226344</v>
       </c>
       <c r="K3">
-        <v>16.6</v>
+        <v>10.3</v>
       </c>
       <c r="L3">
-        <v>0.138218151540383</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
-        <v>14.5</v>
+        <v>2.67</v>
       </c>
       <c r="N3">
-        <v>0.0356090373280943</v>
+        <v>0.01565982404692082</v>
       </c>
       <c r="O3">
-        <v>0.8734939759036143</v>
+        <v>0.2592233009708738</v>
       </c>
       <c r="P3">
-        <v>14.5</v>
+        <v>2.67</v>
       </c>
       <c r="Q3">
-        <v>0.0356090373280943</v>
+        <v>0.01565982404692082</v>
       </c>
       <c r="R3">
-        <v>0.8734939759036143</v>
+        <v>0.2592233009708738</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +767,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>23</v>
+        <v>57.5</v>
       </c>
       <c r="V3">
-        <v>0.05648330058939097</v>
+        <v>0.3372434017595308</v>
       </c>
       <c r="W3">
-        <v>0.4213197969543148</v>
+        <v>0.254950495049505</v>
       </c>
       <c r="X3">
-        <v>0.03663489361391498</v>
+        <v>0.07153833783391207</v>
       </c>
       <c r="Y3">
-        <v>0.3846849033403998</v>
-      </c>
-      <c r="Z3">
-        <v>6.001999000499749</v>
-      </c>
-      <c r="AA3">
-        <v>0.8461252465554663</v>
+        <v>0.1834121572155929</v>
       </c>
       <c r="AB3">
-        <v>0.036128445591989</v>
-      </c>
-      <c r="AC3">
-        <v>0.8099968009634773</v>
+        <v>0.07051393723124263</v>
       </c>
       <c r="AD3">
-        <v>15.8</v>
+        <v>7.35</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.8</v>
+        <v>7.35</v>
       </c>
       <c r="AG3">
-        <v>-7.199999999999999</v>
+        <v>-50.15</v>
       </c>
       <c r="AH3">
-        <v>0.03735224586288416</v>
+        <v>0.04132696092212539</v>
       </c>
       <c r="AI3">
-        <v>0.2472613458528951</v>
+        <v>0.151702786377709</v>
       </c>
       <c r="AJ3">
-        <v>-0.018</v>
+        <v>-0.4167012879102617</v>
       </c>
       <c r="AK3">
-        <v>-0.1760391198044009</v>
+        <v>5.5414364640884</v>
       </c>
       <c r="AL3">
-        <v>0.382</v>
+        <v>0.446</v>
       </c>
       <c r="AM3">
-        <v>0.382</v>
+        <v>0.446</v>
       </c>
       <c r="AN3">
-        <v>0.7085201793721974</v>
+        <v>0.4741935483870968</v>
       </c>
       <c r="AO3">
-        <v>55.23560209424084</v>
+        <v>33.40807174887892</v>
       </c>
       <c r="AP3">
-        <v>-0.3228699551569506</v>
+        <v>-3.235483870967742</v>
       </c>
       <c r="AQ3">
-        <v>55.23560209424084</v>
+        <v>33.40807174887892</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jarvis Securities plc (AIM:JIM)</t>
+          <t>Alpha Group International plc (AIM:ALPH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +844,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.141</v>
+        <v>0.508</v>
       </c>
       <c r="E4">
-        <v>0.192</v>
+        <v>0.477</v>
       </c>
       <c r="G4">
-        <v>0.001386138613861386</v>
+        <v>0.421343146274149</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.421343146274149</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.3983440662373505</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.3198684495016512</v>
       </c>
       <c r="K4">
-        <v>8.800000000000001</v>
+        <v>31.8</v>
       </c>
       <c r="L4">
-        <v>0.4356435643564357</v>
+        <v>0.2925482980680773</v>
       </c>
       <c r="M4">
-        <v>7.98</v>
+        <v>5.59</v>
       </c>
       <c r="N4">
-        <v>0.04705188679245283</v>
+        <v>0.005943015096746757</v>
       </c>
       <c r="O4">
-        <v>0.9068181818181817</v>
+        <v>0.1757861635220126</v>
       </c>
       <c r="P4">
-        <v>7.98</v>
+        <v>5.59</v>
       </c>
       <c r="Q4">
-        <v>0.04705188679245283</v>
+        <v>0.005943015096746757</v>
       </c>
       <c r="R4">
-        <v>0.9068181818181817</v>
+        <v>0.1757861635220126</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,61 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.779999999999999</v>
+        <v>153</v>
       </c>
       <c r="V4">
-        <v>0.05766509433962264</v>
+        <v>0.1626621305549649</v>
       </c>
       <c r="W4">
-        <v>1.060240963855422</v>
+        <v>0.2436781609195402</v>
       </c>
       <c r="X4">
-        <v>0.03599344940302621</v>
+        <v>0.07077599509938312</v>
       </c>
       <c r="Y4">
-        <v>1.024247514452395</v>
+        <v>0.1729021658201571</v>
       </c>
       <c r="Z4">
-        <v>4.926829268292682</v>
+        <v>5.009216589861754</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.602290343817028</v>
       </c>
       <c r="AB4">
-        <v>0.03598218709445222</v>
+        <v>0.07051325715048663</v>
       </c>
       <c r="AC4">
-        <v>-0.03598218709445222</v>
+        <v>1.531777086666541</v>
       </c>
       <c r="AD4">
-        <v>0.148</v>
+        <v>10.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.148</v>
+        <v>10.4</v>
       </c>
       <c r="AG4">
-        <v>-9.632</v>
+        <v>-142.6</v>
       </c>
       <c r="AH4">
-        <v>0.000871880670169899</v>
+        <v>0.01093585699263933</v>
       </c>
       <c r="AI4">
-        <v>0.01100535395597858</v>
+        <v>0.06594800253646163</v>
       </c>
       <c r="AJ4">
-        <v>-0.0602120424084817</v>
+        <v>-0.1786967418546366</v>
       </c>
       <c r="AK4">
-        <v>-2.625954198473281</v>
+        <v>-30.34042553191478</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.637</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>0.235827664399093</v>
+      </c>
+      <c r="AO4">
+        <v>67.97488226059654</v>
+      </c>
+      <c r="AP4">
+        <v>-3.233560090702948</v>
+      </c>
+      <c r="AQ4">
+        <v>77.73788150807898</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AJ Bell plc (LSE:AJB)</t>
+          <t>FRP Advisory Group plc (AIM:FRP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,49 +978,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.176</v>
-      </c>
-      <c r="E5">
-        <v>0.267</v>
+        <v>0.188</v>
       </c>
       <c r="F5">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G5">
-        <v>0.177732379979571</v>
+        <v>0.1733668341708542</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.1733668341708542</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.1641541038525963</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.1294225513532575</v>
       </c>
       <c r="K5">
-        <v>59.2</v>
+        <v>15</v>
       </c>
       <c r="L5">
-        <v>0.3023493360572012</v>
+        <v>0.1256281407035176</v>
       </c>
       <c r="M5">
-        <v>39.3</v>
+        <v>11.5</v>
       </c>
       <c r="N5">
-        <v>0.01865919665748742</v>
+        <v>0.02647329650092081</v>
       </c>
       <c r="O5">
-        <v>0.6638513513513513</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="P5">
-        <v>39.3</v>
+        <v>11.5</v>
       </c>
       <c r="Q5">
-        <v>0.01865919665748742</v>
+        <v>0.02647329650092081</v>
       </c>
       <c r="R5">
-        <v>0.6638513513513513</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,64 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>131</v>
+        <v>31.3</v>
       </c>
       <c r="V5">
-        <v>0.06219732219162473</v>
+        <v>0.07205340699815839</v>
       </c>
       <c r="W5">
-        <v>0.4180790960451978</v>
+        <v>0.3211991434689507</v>
       </c>
       <c r="X5">
-        <v>0.03614811403900819</v>
+        <v>0.07141096375083038</v>
       </c>
       <c r="Y5">
-        <v>0.3819309820061896</v>
+        <v>0.2497881797181203</v>
       </c>
       <c r="Z5">
-        <v>4.23168359628269</v>
+        <v>7.556962025316456</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.9780413057961358</v>
       </c>
       <c r="AB5">
-        <v>0.03601845785881979</v>
+        <v>0.07030373335713712</v>
       </c>
       <c r="AC5">
-        <v>-0.03601845785881979</v>
+        <v>0.9077375724389987</v>
       </c>
       <c r="AD5">
-        <v>21.1</v>
+        <v>16.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>21.1</v>
+        <v>16.4</v>
       </c>
       <c r="AG5">
-        <v>-109.9</v>
+        <v>-14.9</v>
       </c>
       <c r="AH5">
-        <v>0.009918676256287314</v>
+        <v>0.03637976929902396</v>
       </c>
       <c r="AI5">
-        <v>0.1067813765182186</v>
+        <v>0.2268326417704011</v>
       </c>
       <c r="AJ5">
-        <v>-0.05505184591494265</v>
+        <v>-0.03551847437425507</v>
       </c>
       <c r="AK5">
-        <v>-1.65015015015015</v>
+        <v>-0.3634146341463415</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="AM5">
-        <v>-0.031</v>
+        <v>0.621</v>
+      </c>
+      <c r="AN5">
+        <v>0.7922705314009661</v>
+      </c>
+      <c r="AO5">
+        <v>31.56199677938809</v>
+      </c>
+      <c r="AP5">
+        <v>-0.7198067632850242</v>
       </c>
       <c r="AQ5">
-        <v>-0</v>
+        <v>31.56199677938809</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Stanley Group PLC (LSE:CAY)</t>
+          <t>Marechale Capital Plc (AIM:MAC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,113 +1111,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0593</v>
-      </c>
-      <c r="E6">
-        <v>0.503</v>
-      </c>
       <c r="G6">
-        <v>0.0007597535934291581</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.02425093585306393</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.02425093585306393</v>
       </c>
       <c r="K6">
-        <v>14.1</v>
+        <v>1.01</v>
       </c>
       <c r="L6">
-        <v>0.05790554414784394</v>
+        <v>3.014925373134328</v>
       </c>
       <c r="M6">
-        <v>8.44</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02349011967715001</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5985815602836879</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>8.44</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02349011967715001</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.5985815602836879</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>126.2</v>
+        <v>0.284</v>
       </c>
       <c r="V6">
-        <v>0.3512385193431672</v>
+        <v>0.1154471544715447</v>
       </c>
       <c r="W6">
-        <v>0.09450402144772119</v>
+        <v>0.3126934984520124</v>
       </c>
       <c r="X6">
-        <v>0.03650115273403198</v>
+        <v>0.07102911930179508</v>
       </c>
       <c r="Y6">
-        <v>0.05800286871368921</v>
+        <v>0.2416643791502173</v>
       </c>
       <c r="Z6">
-        <v>9.11985018726592</v>
+        <v>0.118989279523726</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.002885601384932172</v>
       </c>
       <c r="AB6">
-        <v>0.03609883879326401</v>
+        <v>0.07057401658769226</v>
       </c>
       <c r="AC6">
-        <v>-0.03609883879326401</v>
+        <v>-0.06768841520276009</v>
       </c>
       <c r="AD6">
-        <v>11.1</v>
+        <v>0.044</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.009379682446117919</v>
       </c>
       <c r="AF6">
-        <v>11.1</v>
+        <v>0.05337968244611792</v>
       </c>
       <c r="AG6">
-        <v>-115.1</v>
+        <v>-0.2306203175538821</v>
       </c>
       <c r="AH6">
-        <v>0.02996760259179265</v>
+        <v>0.02123820878275214</v>
       </c>
       <c r="AI6">
-        <v>0.06092206366630077</v>
+        <v>0.0132673738645676</v>
       </c>
       <c r="AJ6">
-        <v>-0.4713349713349714</v>
+        <v>-0.103445958250073</v>
       </c>
       <c r="AK6">
-        <v>-2.055357142857143</v>
+        <v>-0.0616734156834862</v>
       </c>
       <c r="AL6">
-        <v>0.158</v>
+        <v>1.74</v>
       </c>
       <c r="AM6">
-        <v>0.158</v>
+        <v>1.74</v>
+      </c>
+      <c r="AN6">
+        <v>4.399999999999999</v>
       </c>
       <c r="AO6">
         <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>-23.06203175538821</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -1225,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IG Group Holdings plc (LSE:IGG)</t>
+          <t>Numis Corporation Plc (AIM:NUM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1234,13 +1237,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.117</v>
+        <v>0.0105</v>
       </c>
       <c r="E7">
-        <v>0.177</v>
+        <v>-0.147</v>
       </c>
       <c r="G7">
-        <v>0.005502471169686985</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1252,91 +1255,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>528.4</v>
+        <v>15.3</v>
       </c>
       <c r="L7">
-        <v>0.4352553542009884</v>
+        <v>0.09763880025526485</v>
       </c>
       <c r="M7">
-        <v>227.184</v>
+        <v>30.3</v>
       </c>
       <c r="N7">
-        <v>0.04791799371453882</v>
+        <v>0.1212970376301041</v>
       </c>
       <c r="O7">
-        <v>0.4299470098410295</v>
+        <v>1.980392156862745</v>
       </c>
       <c r="P7">
-        <v>226.9</v>
+        <v>17.4</v>
       </c>
       <c r="Q7">
-        <v>0.04785809200396532</v>
+        <v>0.06965572457966372</v>
       </c>
       <c r="R7">
-        <v>0.4294095382286147</v>
+        <v>1.137254901960784</v>
       </c>
       <c r="S7">
-        <v>0.2839999999999918</v>
+        <v>12.9</v>
       </c>
       <c r="T7">
-        <v>0.001250088034368581</v>
+        <v>0.4257425742574257</v>
       </c>
       <c r="U7">
-        <v>930.9</v>
+        <v>117.7</v>
       </c>
       <c r="V7">
-        <v>0.1963468393410812</v>
+        <v>0.4711769415532426</v>
       </c>
       <c r="W7">
-        <v>0.457449571465674</v>
+        <v>0.06069020230067434</v>
       </c>
       <c r="X7">
-        <v>0.03659650455370415</v>
+        <v>0.07492147663012844</v>
       </c>
       <c r="Y7">
-        <v>0.4208530669119698</v>
+        <v>-0.0142312743294541</v>
       </c>
       <c r="Z7">
-        <v>2.090220385674932</v>
+        <v>1.25259792166267</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03611999346590527</v>
+        <v>0.06961349734950266</v>
       </c>
       <c r="AC7">
-        <v>-0.03611999346590527</v>
+        <v>-0.06961349734950266</v>
       </c>
       <c r="AD7">
-        <v>173.2</v>
+        <v>46.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>173.2</v>
+        <v>46.3</v>
       </c>
       <c r="AG7">
-        <v>-757.7</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.03524408359278025</v>
+        <v>0.1563660925363053</v>
       </c>
       <c r="AI7">
-        <v>0.09712331071608815</v>
+        <v>0.1832212109220419</v>
       </c>
       <c r="AJ7">
-        <v>-0.1902143897173269</v>
+        <v>-0.4002242152466368</v>
       </c>
       <c r="AK7">
-        <v>-0.8889019239793526</v>
+        <v>-0.528888888888889</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-2.98</v>
+        <v>-0.532</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1350,7 +1353,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CMC Markets plc (LSE:CMCX)</t>
+          <t>Walker Crips Group plc (LSE:WCW)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1359,10 +1362,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.129</v>
+        <v>0.0105</v>
       </c>
       <c r="E8">
-        <v>0.207</v>
+        <v>-0.238</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,91 +1380,94 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>128.5</v>
+        <v>0.274</v>
       </c>
       <c r="L8">
-        <v>0.3132618235007313</v>
+        <v>0.007425474254742549</v>
       </c>
       <c r="M8">
-        <v>120.598</v>
+        <v>0.202</v>
       </c>
       <c r="N8">
-        <v>0.1161159252840362</v>
+        <v>0.01337748344370861</v>
       </c>
       <c r="O8">
-        <v>0.9385058365758755</v>
+        <v>0.7372262773722628</v>
       </c>
       <c r="P8">
-        <v>120.4</v>
+        <v>0.202</v>
       </c>
       <c r="Q8">
-        <v>0.1159252840362026</v>
+        <v>0.01337748344370861</v>
       </c>
       <c r="R8">
-        <v>0.9369649805447471</v>
+        <v>0.7372262773722628</v>
       </c>
       <c r="S8">
-        <v>0.1979999999999933</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.001641818272276433</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>177.7</v>
+        <v>11.8</v>
       </c>
       <c r="V8">
-        <v>0.1710957057577508</v>
+        <v>0.7814569536423842</v>
       </c>
       <c r="W8">
-        <v>0.2755736650225177</v>
+        <v>0.009163879598662208</v>
       </c>
       <c r="X8">
-        <v>0.03638902836546368</v>
+        <v>0.0748131709057745</v>
       </c>
       <c r="Y8">
-        <v>0.239184636657054</v>
+        <v>-0.06564929130711229</v>
       </c>
       <c r="Z8">
-        <v>1.356481481481482</v>
+        <v>2.151603498542274</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03616227097178666</v>
+        <v>0.06963221270784434</v>
       </c>
       <c r="AC8">
-        <v>-0.03616227097178666</v>
+        <v>-0.06963221270784434</v>
       </c>
       <c r="AD8">
-        <v>25.2</v>
+        <v>2.73</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>25.2</v>
+        <v>2.73</v>
       </c>
       <c r="AG8">
-        <v>-152.5</v>
+        <v>-9.07</v>
       </c>
       <c r="AH8">
-        <v>0.02368866328257191</v>
+        <v>0.1531127313516545</v>
       </c>
       <c r="AI8">
-        <v>0.04862987263604785</v>
+        <v>0.1013739324173784</v>
       </c>
       <c r="AJ8">
-        <v>-0.1721024715043449</v>
+        <v>-1.504145936981758</v>
       </c>
       <c r="AK8">
-        <v>-0.447870778267254</v>
+        <v>-0.5994712491738269</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-0.041</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1478,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Numis Corporation Plc (AIM:NUM)</t>
+          <t>IG Group Holdings plc (LSE:IGG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,10 +1487,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.139</v>
+        <v>0.131</v>
       </c>
       <c r="E9">
-        <v>0.17</v>
+        <v>0.244</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,91 +1505,91 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>78.09999999999999</v>
+        <v>634.8</v>
       </c>
       <c r="L9">
-        <v>0.2596409574468085</v>
+        <v>0.5219965463366499</v>
       </c>
       <c r="M9">
-        <v>49.90000000000001</v>
+        <v>243.04</v>
       </c>
       <c r="N9">
-        <v>0.09725199766127461</v>
+        <v>0.06207284057822955</v>
       </c>
       <c r="O9">
-        <v>0.6389244558258644</v>
+        <v>0.3828607435412729</v>
       </c>
       <c r="P9">
-        <v>17.2</v>
+        <v>234.6</v>
       </c>
       <c r="Q9">
-        <v>0.03352173065679204</v>
+        <v>0.05991724983398886</v>
       </c>
       <c r="R9">
-        <v>0.2202304737516005</v>
+        <v>0.3695652173913044</v>
       </c>
       <c r="S9">
-        <v>32.7</v>
+        <v>8.439999999999998</v>
       </c>
       <c r="T9">
-        <v>0.655310621242485</v>
+        <v>0.03472679394338379</v>
       </c>
       <c r="U9">
-        <v>181.1</v>
+        <v>1570.3</v>
       </c>
       <c r="V9">
-        <v>0.3529526408107581</v>
+        <v>0.4010573632323645</v>
       </c>
       <c r="W9">
-        <v>0.3832188420019627</v>
+        <v>0.3942612260108068</v>
       </c>
       <c r="X9">
-        <v>0.03776182373438452</v>
+        <v>0.07295502940296564</v>
       </c>
       <c r="Y9">
-        <v>0.3454570182675781</v>
+        <v>0.3213061966078411</v>
       </c>
       <c r="Z9">
-        <v>6.286311389759667</v>
+        <v>1.737285714285714</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03636109599825504</v>
+        <v>0.06997737658762625</v>
       </c>
       <c r="AC9">
-        <v>-0.03636109599825504</v>
+        <v>-0.06997737658762625</v>
       </c>
       <c r="AD9">
-        <v>54.1</v>
+        <v>402</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>54.1</v>
+        <v>402</v>
       </c>
       <c r="AG9">
-        <v>-127</v>
+        <v>-1168.3</v>
       </c>
       <c r="AH9">
-        <v>0.09538081805359661</v>
+        <v>0.09311159494139992</v>
       </c>
       <c r="AI9">
-        <v>0.1766819072501633</v>
+        <v>0.1359623905029256</v>
       </c>
       <c r="AJ9">
-        <v>-0.3289303289303289</v>
+        <v>-0.4252848458374285</v>
       </c>
       <c r="AK9">
-        <v>-1.015187849720224</v>
+        <v>-0.8426860934795154</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.001</v>
+        <v>-4.28</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1597,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cenkos Securities plc (AIM:CNKS)</t>
+          <t>Fiske plc (AIM:FKE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1605,12 +1611,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D10">
-        <v>-0.008289999999999999</v>
-      </c>
-      <c r="E10">
-        <v>0.143</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1624,91 +1624,88 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>-0.193</v>
       </c>
       <c r="L10">
-        <v>0.07338551859099804</v>
+        <v>-0.03001555209953344</v>
       </c>
       <c r="M10">
-        <v>5.970000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.118452380952381</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>1.592</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.47</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04900793650793651</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.6586666666666667</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
-      </c>
-      <c r="T10">
-        <v>0.5862646566164155</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>33.1</v>
+        <v>4.79</v>
       </c>
       <c r="V10">
-        <v>0.6567460317460317</v>
+        <v>0.4974039460020768</v>
       </c>
       <c r="W10">
-        <v>0.1233552631578947</v>
+        <v>-0.0187378640776699</v>
       </c>
       <c r="X10">
-        <v>0.03815976911252321</v>
+        <v>0.07152071563074222</v>
       </c>
       <c r="Y10">
-        <v>0.08519549404537154</v>
+        <v>-0.09025857970841213</v>
       </c>
       <c r="Z10">
-        <v>5.362014690451208</v>
+        <v>1.015156299336912</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03643668892521642</v>
+        <v>0.07027919394934221</v>
       </c>
       <c r="AC10">
-        <v>-0.03643668892521642</v>
+        <v>-0.07027919394934221</v>
       </c>
       <c r="AD10">
-        <v>6.5</v>
+        <v>0.408</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>6.5</v>
+        <v>0.408</v>
       </c>
       <c r="AG10">
-        <v>-26.6</v>
+        <v>-4.382</v>
       </c>
       <c r="AH10">
-        <v>0.1142355008787346</v>
+        <v>0.04064554692169754</v>
       </c>
       <c r="AI10">
-        <v>0.15625</v>
+        <v>0.03882755995432052</v>
       </c>
       <c r="AJ10">
-        <v>-1.11764705882353</v>
+        <v>-0.8349847560975607</v>
       </c>
       <c r="AK10">
-        <v>-3.129411764705882</v>
+        <v>-0.7663518712836656</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.019</v>
+        <v>-0.208</v>
       </c>
       <c r="AQ10">
         <v>-0</v>
@@ -1722,7 +1719,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arden Partners plc (AIM:ARDN)</t>
+          <t>AJ Bell plc (LSE:AJB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1731,10 +1728,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.09449999999999999</v>
+        <v>0.167</v>
+      </c>
+      <c r="E11">
+        <v>0.216</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.2003302146395157</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1746,91 +1746,91 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1.53</v>
+        <v>52.1</v>
       </c>
       <c r="L11">
-        <v>0.1285714285714286</v>
+        <v>0.28673637864612</v>
       </c>
       <c r="M11">
-        <v>0.43</v>
+        <v>33.3</v>
       </c>
       <c r="N11">
-        <v>0.05361596009975063</v>
+        <v>0.01877325515841696</v>
       </c>
       <c r="O11">
-        <v>0.2810457516339869</v>
+        <v>0.6391554702495201</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>33.3</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.01877325515841696</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.6391554702495201</v>
       </c>
       <c r="S11">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>4.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V11">
-        <v>0.5361596009975063</v>
+        <v>0.0527680685533882</v>
       </c>
       <c r="W11">
-        <v>0.2693661971830986</v>
+        <v>0.2951841359773371</v>
       </c>
       <c r="X11">
-        <v>0.03763612639701162</v>
+        <v>0.07072219173372495</v>
       </c>
       <c r="Y11">
-        <v>0.231730070786087</v>
+        <v>0.2244619442436122</v>
       </c>
       <c r="Z11">
-        <v>3.918340467566678</v>
+        <v>2.966046359777996</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03667040682436338</v>
+        <v>0.07046286103539223</v>
       </c>
       <c r="AC11">
-        <v>-0.03667040682436338</v>
+        <v>-0.07046286103539223</v>
       </c>
       <c r="AD11">
-        <v>0.786</v>
+        <v>15.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.786</v>
+        <v>15.6</v>
       </c>
       <c r="AG11">
-        <v>-3.514</v>
+        <v>-78</v>
       </c>
       <c r="AH11">
-        <v>0.08925732455144221</v>
+        <v>0.00871800603554264</v>
       </c>
       <c r="AI11">
-        <v>0.09372764130694015</v>
+        <v>0.09500609013398295</v>
       </c>
       <c r="AJ11">
-        <v>-0.779849090102086</v>
+        <v>-0.04599599009317137</v>
       </c>
       <c r="AK11">
-        <v>-0.8600097895252079</v>
+        <v>-1.104815864022663</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.043</v>
+        <v>-0.221</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>finnCap Group plc (AIM:FCAP)</t>
+          <t>Jarvis Securities plc (AIM:JIM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1852,8 +1852,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.0621</v>
+      </c>
+      <c r="E12">
+        <v>0.0765</v>
+      </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.002251655629139073</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1865,94 +1871,91 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>6.04</v>
       </c>
       <c r="L12">
-        <v>0.1552393272962484</v>
+        <v>0.4</v>
       </c>
       <c r="M12">
-        <v>3.422</v>
+        <v>7.08</v>
       </c>
       <c r="N12">
-        <v>0.046812585499316</v>
+        <v>0.08082191780821918</v>
       </c>
       <c r="O12">
-        <v>0.2851666666666666</v>
+        <v>1.172185430463576</v>
       </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>7.08</v>
       </c>
       <c r="Q12">
-        <v>0.04514363885088919</v>
+        <v>0.08082191780821918</v>
       </c>
       <c r="R12">
-        <v>0.275</v>
+        <v>1.172185430463576</v>
       </c>
       <c r="S12">
-        <v>0.1219999999999999</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.03565166569257741</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>30.5</v>
+        <v>5.07</v>
       </c>
       <c r="V12">
-        <v>0.4172366621067032</v>
+        <v>0.05787671232876713</v>
       </c>
       <c r="W12">
-        <v>0.3883495145631068</v>
+        <v>0.4541353383458646</v>
       </c>
       <c r="X12">
-        <v>0.04074451705210468</v>
+        <v>0.0705203433509391</v>
       </c>
       <c r="Y12">
-        <v>0.3476049975110021</v>
+        <v>0.3836149949949255</v>
       </c>
       <c r="Z12">
-        <v>4.36723163841808</v>
+        <v>4.72761427676894</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03686012503197539</v>
+        <v>0.07051301932705765</v>
       </c>
       <c r="AC12">
-        <v>-0.03686012503197539</v>
+        <v>-0.07051301932705765</v>
       </c>
       <c r="AD12">
-        <v>20.6</v>
+        <v>0.027</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>20.6</v>
+        <v>0.027</v>
       </c>
       <c r="AG12">
-        <v>-9.899999999999999</v>
+        <v>-5.043</v>
       </c>
       <c r="AH12">
-        <v>0.2198505869797226</v>
+        <v>0.0003081242082919648</v>
       </c>
       <c r="AI12">
-        <v>0.3179012345679012</v>
+        <v>0.004442981734408425</v>
       </c>
       <c r="AJ12">
-        <v>-0.1566455696202531</v>
+        <v>-0.06108506849812858</v>
       </c>
       <c r="AK12">
-        <v>-0.2886297376093294</v>
+        <v>-5.007944389275076</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.018</v>
-      </c>
-      <c r="AQ12">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1963,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Walker Crips Group plc (LSE:WCW)</t>
+          <t>CMC Markets plc (LSE:CMCX)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1972,13 +1975,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0396</v>
+        <v>0.119</v>
       </c>
       <c r="E13">
-        <v>-0.167</v>
+        <v>0.081</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.0005509964830011724</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1990,94 +1993,91 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.205</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L13">
-        <v>0.004812206572769952</v>
+        <v>0.2385697538100821</v>
       </c>
       <c r="M13">
-        <v>0.359</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N13">
-        <v>0.01860103626943005</v>
+        <v>0.09503583753650119</v>
       </c>
       <c r="O13">
-        <v>1.751219512195122</v>
+        <v>0.8796068796068794</v>
       </c>
       <c r="P13">
-        <v>0.359</v>
+        <v>39.5</v>
       </c>
       <c r="Q13">
-        <v>0.01860103626943005</v>
+        <v>0.05242898858508097</v>
       </c>
       <c r="R13">
-        <v>1.751219512195122</v>
+        <v>0.4852579852579852</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>32.09999999999999</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.4483240223463686</v>
       </c>
       <c r="U13">
-        <v>11.3</v>
+        <v>157</v>
       </c>
       <c r="V13">
-        <v>0.5854922279792746</v>
+        <v>0.208388638173613</v>
       </c>
       <c r="W13">
-        <v>0.007118055555555555</v>
+        <v>0.1651115618661258</v>
       </c>
       <c r="X13">
-        <v>0.03989555568105604</v>
+        <v>0.07115703830163905</v>
       </c>
       <c r="Y13">
-        <v>-0.03277750012550049</v>
+        <v>0.09395452356448672</v>
       </c>
       <c r="Z13">
-        <v>2.292787944025835</v>
+        <v>1.002055800293685</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03790011839985943</v>
+        <v>0.07051360238230464</v>
       </c>
       <c r="AC13">
-        <v>-0.03790011839985943</v>
+        <v>-0.07051360238230464</v>
       </c>
       <c r="AD13">
-        <v>4.47</v>
+        <v>20.4</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>4.47</v>
+        <v>20.4</v>
       </c>
       <c r="AG13">
-        <v>-6.830000000000001</v>
+        <v>-136.6</v>
       </c>
       <c r="AH13">
-        <v>0.1880521665965503</v>
+        <v>0.02636340139570948</v>
       </c>
       <c r="AI13">
-        <v>0.1300552807681117</v>
+        <v>0.0463004993191103</v>
       </c>
       <c r="AJ13">
-        <v>-0.5477145148356056</v>
+        <v>-0.2214656290531777</v>
       </c>
       <c r="AK13">
-        <v>-0.2960554833116603</v>
+        <v>-0.4816643159379407</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.011</v>
-      </c>
-      <c r="AQ13">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Craven House Capital Plc (AIM:CRV)</t>
+          <t>Cenkos Securities plc (AIM:CNKS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2096,86 +2096,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.114</v>
+      </c>
+      <c r="E14">
+        <v>-0.22</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
       <c r="K14">
-        <v>-2.43</v>
+        <v>1.83</v>
+      </c>
+      <c r="L14">
+        <v>0.04778067885117494</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>7.78</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.3228215767634855</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.251366120218579</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>2.66</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.1103734439834025</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.453551912568306</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>5.12</v>
+      </c>
+      <c r="T14">
+        <v>0.6580976863753213</v>
       </c>
       <c r="U14">
-        <v>0.005</v>
+        <v>19.3</v>
       </c>
       <c r="V14">
-        <v>0.005175983436853002</v>
+        <v>0.8008298755186721</v>
       </c>
       <c r="W14">
-        <v>-0.3115384615384615</v>
+        <v>0.05213675213675214</v>
       </c>
       <c r="X14">
-        <v>0.05329309212428258</v>
+        <v>0.07656282880773614</v>
       </c>
       <c r="Y14">
-        <v>-0.3648315536627441</v>
+        <v>-0.024426076670984</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.505882352941176</v>
       </c>
       <c r="AA14">
-        <v>-0.0266871952784193</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04114755487139025</v>
+        <v>0.07051755013779436</v>
       </c>
       <c r="AC14">
-        <v>-0.06783475014980955</v>
+        <v>-0.07051755013779436</v>
       </c>
       <c r="AD14">
-        <v>0.989</v>
+        <v>6.13</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.989</v>
+        <v>6.13</v>
       </c>
       <c r="AG14">
-        <v>0.984</v>
+        <v>-13.17</v>
       </c>
       <c r="AH14">
-        <v>0.5058823529411764</v>
+        <v>0.2027786966589481</v>
       </c>
       <c r="AI14">
-        <v>0.1555275986790376</v>
+        <v>0.1754938448325222</v>
       </c>
       <c r="AJ14">
-        <v>0.5046153846153846</v>
+        <v>-1.204940530649588</v>
       </c>
       <c r="AK14">
-        <v>0.1548630783758262</v>
+        <v>-0.8426103646833015</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.068</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2186,7 +2213,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marechale Capital Plc (AIM:MAC)</t>
+          <t>finnCap Group plc (AIM:FCAP)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2201,100 +2228,97 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.008233156419510619</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.008233156419510619</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>2.48</v>
+        <v>-1.52</v>
       </c>
       <c r="L15">
-        <v>2.517766497461929</v>
+        <v>-0.03725490196078432</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>2.059</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.0830241935483871</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>-1.354605263157895</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>1.12</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.04516129032258065</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>-0.736842105263158</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>0.9390000000000001</v>
+      </c>
+      <c r="T15">
+        <v>0.4560466245750364</v>
       </c>
       <c r="U15">
-        <v>0.49</v>
+        <v>12.4</v>
       </c>
       <c r="V15">
-        <v>0.1346153846153846</v>
+        <v>0.5</v>
       </c>
       <c r="W15">
-        <v>19.375</v>
+        <v>-0.03438914027149321</v>
       </c>
       <c r="X15">
-        <v>0.03632924635753198</v>
+        <v>0.08317264239473134</v>
       </c>
       <c r="Y15">
-        <v>19.33867075364247</v>
+        <v>-0.1175617826662246</v>
       </c>
       <c r="Z15">
-        <v>-37.10219381008329</v>
+        <v>1.189504373177842</v>
       </c>
       <c r="AA15">
-        <v>-0.3054681651454144</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03654570495945007</v>
+        <v>0.07052078571256343</v>
       </c>
       <c r="AC15">
-        <v>-0.3420138701048644</v>
+        <v>-0.07052078571256343</v>
       </c>
       <c r="AD15">
-        <v>0.066</v>
+        <v>13.2</v>
       </c>
       <c r="AE15">
-        <v>0.009451704633910202</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.07545170463391021</v>
+        <v>13.2</v>
       </c>
       <c r="AG15">
-        <v>-0.4145482953660898</v>
+        <v>0.7999999999999989</v>
       </c>
       <c r="AH15">
-        <v>0.02030754552395524</v>
+        <v>0.3473684210526315</v>
       </c>
       <c r="AI15">
-        <v>0.02282644291191262</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="AJ15">
-        <v>-0.1285241055603222</v>
+        <v>0.03124999999999996</v>
       </c>
       <c r="AK15">
-        <v>-0.1472404213802676</v>
+        <v>0.02292263610315183</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-2.08</v>
-      </c>
-      <c r="AN15">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="AP15">
-        <v>-41.45482953660898</v>
+        <v>-0.031</v>
       </c>
       <c r="AQ15">
         <v>-0</v>
@@ -2308,7 +2332,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alpha FX Group plc (AIM:AFX)</t>
+          <t>Craven House Capital Plc (AIM:CRV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2316,116 +2340,92 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G16">
-        <v>0.308584686774942</v>
-      </c>
-      <c r="H16">
-        <v>0.308584686774942</v>
-      </c>
-      <c r="I16">
-        <v>0.4559164733178654</v>
-      </c>
-      <c r="J16">
-        <v>0.3671139435280149</v>
-      </c>
       <c r="K16">
-        <v>28</v>
-      </c>
-      <c r="L16">
-        <v>0.3248259860788863</v>
+        <v>-0.236</v>
       </c>
       <c r="M16">
-        <v>4.52</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.003729372937293729</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.1614285714285714</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>4.52</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.003729372937293729</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.1614285714285714</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>118.9</v>
+        <v>0.001</v>
       </c>
       <c r="V16">
-        <v>0.0981023102310231</v>
+        <v>0.003048780487804878</v>
       </c>
       <c r="W16">
-        <v>0.2904564315352697</v>
+        <v>-0.04394785847299813</v>
       </c>
       <c r="X16">
-        <v>0.03611962268433037</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="Y16">
-        <v>0.2543368088509393</v>
+        <v>-0.1144608709049675</v>
       </c>
       <c r="Z16">
-        <v>-2.236057068741894</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>-0.82088772845953</v>
+        <v>-0.02832861189801699</v>
       </c>
       <c r="AB16">
-        <v>0.03604273842215372</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="AC16">
-        <v>-0.8569304668816837</v>
+        <v>-0.09884162432998636</v>
       </c>
       <c r="AD16">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>-108.8</v>
+        <v>-0.001</v>
       </c>
       <c r="AH16">
-        <v>0.008264462809917356</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.06908344733242135</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.09862218999274837</v>
+        <v>-0.003058103975535168</v>
       </c>
       <c r="AK16">
-        <v>-3.985347985347988</v>
+        <v>-0.000194969779684149</v>
       </c>
       <c r="AL16">
-        <v>0.834</v>
+        <v>0.056</v>
       </c>
       <c r="AM16">
-        <v>0.83</v>
-      </c>
-      <c r="AN16">
-        <v>0.2525</v>
+        <v>0.056</v>
       </c>
       <c r="AO16">
-        <v>47.12230215827338</v>
-      </c>
-      <c r="AP16">
-        <v>-2.72</v>
+        <v>-3.214285714285714</v>
       </c>
       <c r="AQ16">
-        <v>47.34939759036144</v>
+        <v>-3.214285714285714</v>
       </c>
     </row>
     <row r="17">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Argentum 47, Inc. (OTCPK:ARGQ)</t>
+          <t>Hamilton Global Opportunities PLC (ENXTPA:ALHGO)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2444,26 +2444,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D17">
-        <v>-0.482</v>
-      </c>
       <c r="G17">
-        <v>0</v>
+        <v>-1.37037037037037</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>-1.37037037037037</v>
       </c>
       <c r="I17">
-        <v>-5.197802197802198</v>
+        <v>-0.3518518518518519</v>
       </c>
       <c r="J17">
-        <v>-5.197802197802198</v>
+        <v>-0.2687268518518519</v>
       </c>
       <c r="K17">
-        <v>-0.584</v>
+        <v>1.83</v>
       </c>
       <c r="L17">
-        <v>-6.417582417582417</v>
+        <v>8.472222222222223</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2472,7 +2469,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2481,207 +2478,73 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.047</v>
+        <v>3.56</v>
       </c>
       <c r="V17">
-        <v>0.01012931034482759</v>
+        <v>0.1663551401869159</v>
       </c>
       <c r="W17">
-        <v>1.031802120141343</v>
+        <v>0.1694444444444445</v>
       </c>
       <c r="X17">
-        <v>0.04049820827505595</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="Y17">
-        <v>0.9913039118662869</v>
+        <v>0.09893143201247509</v>
       </c>
       <c r="Z17">
-        <v>0.2916666666666666</v>
+        <v>1.079999999999994</v>
       </c>
       <c r="AA17">
-        <v>-1.516025641025641</v>
+        <v>-0.2902249999999985</v>
       </c>
       <c r="AB17">
-        <v>0.03909262862127341</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="AC17">
-        <v>-1.555118269646914</v>
+        <v>-0.3607380124319678</v>
       </c>
       <c r="AD17">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.193</v>
+        <v>-3.56</v>
       </c>
       <c r="AH17">
-        <v>0.2108843537414966</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>8.857142857142863</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>0.2045259729127379</v>
+        <v>-0.1995515695067265</v>
       </c>
       <c r="AK17">
-        <v>12.82795698924732</v>
+        <v>-0.3058419243986255</v>
       </c>
       <c r="AL17">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>-2.767857142857143</v>
-      </c>
-      <c r="AO17">
-        <v>-7.390624999999999</v>
+        <v>-0</v>
       </c>
       <c r="AP17">
-        <v>-2.662946428571429</v>
-      </c>
-      <c r="AQ17">
-        <v>-7.390624999999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Argentex Group Plc (AIM:AGFX)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>0.3185185185185185</v>
-      </c>
-      <c r="H18">
-        <v>0.2777777777777777</v>
-      </c>
-      <c r="I18">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="J18">
-        <v>0.2349015682349015</v>
-      </c>
-      <c r="K18">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="L18">
-        <v>0.2032407407407407</v>
-      </c>
-      <c r="M18">
-        <v>2.97</v>
-      </c>
-      <c r="N18">
-        <v>0.02094499294781382</v>
-      </c>
-      <c r="O18">
-        <v>0.3382687927107062</v>
-      </c>
-      <c r="P18">
-        <v>2.97</v>
-      </c>
-      <c r="Q18">
-        <v>0.02094499294781382</v>
-      </c>
-      <c r="R18">
-        <v>0.3382687927107062</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>59</v>
-      </c>
-      <c r="V18">
-        <v>0.4160789844851904</v>
-      </c>
-      <c r="W18">
-        <v>0.2660606060606061</v>
-      </c>
-      <c r="X18">
-        <v>0.03762454492824697</v>
-      </c>
-      <c r="Y18">
-        <v>0.2284360611323591</v>
-      </c>
-      <c r="Z18">
-        <v>-39.27272727272722</v>
-      </c>
-      <c r="AA18">
-        <v>-9.225225225225214</v>
-      </c>
-      <c r="AB18">
-        <v>0.03633426668487395</v>
-      </c>
-      <c r="AC18">
-        <v>-9.261559491910088</v>
-      </c>
-      <c r="AD18">
-        <v>13.8</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>13.8</v>
-      </c>
-      <c r="AG18">
-        <v>-45.2</v>
-      </c>
-      <c r="AH18">
-        <v>0.08868894601542415</v>
-      </c>
-      <c r="AI18">
-        <v>0.2546125461254612</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.4679089026915114</v>
-      </c>
-      <c r="AK18">
-        <v>9.416666666666659</v>
-      </c>
-      <c r="AL18">
-        <v>0.54</v>
-      </c>
-      <c r="AM18">
-        <v>0.54</v>
-      </c>
-      <c r="AN18">
-        <v>1.029850746268657</v>
-      </c>
-      <c r="AO18">
-        <v>23.7037037037037</v>
-      </c>
-      <c r="AP18">
-        <v>-3.373134328358209</v>
-      </c>
-      <c r="AQ18">
-        <v>23.7037037037037</v>
+        <v>48.10810810810811</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ17"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.119</v>
+        <v>0.0891</v>
       </c>
       <c r="E2">
-        <v>0.07875</v>
-      </c>
-      <c r="F2">
-        <v>0.03</v>
+        <v>0.09995000000000001</v>
       </c>
       <c r="G2">
-        <v>0.05156349083873344</v>
+        <v>0.06229007843369634</v>
       </c>
       <c r="H2">
-        <v>0.03505864360431767</v>
+        <v>0.03988456085116835</v>
       </c>
       <c r="I2">
-        <v>0.03352328218460806</v>
+        <v>0.06105303369314984</v>
       </c>
       <c r="J2">
-        <v>0.02780904834564419</v>
+        <v>0.05188645972619248</v>
       </c>
       <c r="K2">
-        <v>849.735</v>
+        <v>651.8140000000001</v>
       </c>
       <c r="L2">
-        <v>0.367313036633395</v>
+        <v>0.2798871200586042</v>
       </c>
       <c r="M2">
-        <v>415.121</v>
+        <v>572.953</v>
       </c>
       <c r="N2">
-        <v>0.04928236117881338</v>
+        <v>0.07764990167604731</v>
       </c>
       <c r="O2">
-        <v>0.4885299534560775</v>
+        <v>0.8790130313248871</v>
       </c>
       <c r="P2">
-        <v>355.622</v>
+        <v>330.933</v>
       </c>
       <c r="Q2">
-        <v>0.04221875512713637</v>
+        <v>0.04484995263374023</v>
       </c>
       <c r="R2">
-        <v>0.4185092999582223</v>
+        <v>0.5077107886605687</v>
       </c>
       <c r="S2">
-        <v>59.49899999999999</v>
+        <v>242.02</v>
       </c>
       <c r="T2">
-        <v>0.1433292943503219</v>
+        <v>0.4224081207359068</v>
       </c>
       <c r="U2">
-        <v>2237.605</v>
+        <v>1666.403</v>
       </c>
       <c r="V2">
-        <v>0.2656441321578979</v>
+        <v>0.2258405647630264</v>
       </c>
       <c r="W2">
-        <v>0.1694444444444445</v>
+        <v>0.1032388493498568</v>
       </c>
       <c r="X2">
-        <v>0.07141096375083038</v>
+        <v>0.06040893228047791</v>
       </c>
       <c r="Y2">
-        <v>0.09803348069361408</v>
+        <v>0.04282991706937885</v>
       </c>
       <c r="Z2">
-        <v>1.722281335698823</v>
+        <v>2.193445831456827</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07051301243196936</v>
+        <v>0.05994536850011643</v>
       </c>
       <c r="AC2">
-        <v>-0.07027919394934221</v>
+        <v>-0.059641039934449</v>
       </c>
       <c r="AD2">
-        <v>540.989</v>
+        <v>493.467</v>
       </c>
       <c r="AE2">
-        <v>0.009379682446117919</v>
+        <v>0.009433479213692104</v>
       </c>
       <c r="AF2">
-        <v>540.9983796824461</v>
+        <v>493.4764334792137</v>
       </c>
       <c r="AG2">
-        <v>-1696.606620317554</v>
+        <v>-1172.926566520786</v>
       </c>
       <c r="AH2">
-        <v>0.06035021040852762</v>
+        <v>0.06268638898541352</v>
       </c>
       <c r="AI2">
-        <v>0.1275113042935009</v>
+        <v>0.1209451725866044</v>
       </c>
       <c r="AJ2">
-        <v>-0.2522193274773218</v>
+        <v>-0.1890066160635958</v>
       </c>
       <c r="AK2">
-        <v>-0.8461273330918835</v>
+        <v>-0.4859326934247747</v>
       </c>
       <c r="AL2">
-        <v>3.5</v>
+        <v>2.549</v>
       </c>
       <c r="AM2">
-        <v>-1.961</v>
+        <v>-42.845</v>
       </c>
       <c r="AN2">
-        <v>6.742472206989381</v>
+        <v>3.387498026401598</v>
       </c>
       <c r="AO2">
-        <v>22.15542857142857</v>
+        <v>55.77677520596312</v>
       </c>
       <c r="AP2">
-        <v>-21.14520440098651</v>
+        <v>-8.051777381675302</v>
       </c>
       <c r="AQ2">
-        <v>-39.54309026007139</v>
+        <v>-3.318356867779204</v>
       </c>
     </row>
     <row r="3">
@@ -725,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3196116504854369</v>
+        <v>0.2177777777777778</v>
       </c>
       <c r="H3">
-        <v>0.2893203883495146</v>
+        <v>0.1934640522875817</v>
       </c>
       <c r="I3">
-        <v>0.2893203883495146</v>
+        <v>0.2052287581699346</v>
       </c>
       <c r="J3">
-        <v>0.221956238226344</v>
+        <v>0.183377063055438</v>
       </c>
       <c r="K3">
-        <v>10.3</v>
+        <v>12.4</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.1620915032679739</v>
       </c>
       <c r="M3">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="N3">
-        <v>0.01565982404692082</v>
+        <v>0.01078582434514638</v>
       </c>
       <c r="O3">
-        <v>0.2592233009708738</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="P3">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>0.01565982404692082</v>
+        <v>0.01078582434514638</v>
       </c>
       <c r="R3">
-        <v>0.2592233009708738</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,64 +764,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>57.5</v>
+        <v>41.4</v>
       </c>
       <c r="V3">
-        <v>0.3372434017595308</v>
-      </c>
-      <c r="W3">
-        <v>0.254950495049505</v>
+        <v>0.3189522342064715</v>
       </c>
       <c r="X3">
-        <v>0.07153833783391207</v>
-      </c>
-      <c r="Y3">
-        <v>0.1834121572155929</v>
+        <v>0.06183979838944288</v>
       </c>
       <c r="AB3">
-        <v>0.07051393723124263</v>
+        <v>0.05989219759771094</v>
       </c>
       <c r="AD3">
-        <v>7.35</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.35</v>
+        <v>15</v>
       </c>
       <c r="AG3">
-        <v>-50.15</v>
+        <v>-26.4</v>
       </c>
       <c r="AH3">
-        <v>0.04132696092212539</v>
+        <v>0.1035911602209945</v>
       </c>
       <c r="AI3">
-        <v>0.151702786377709</v>
+        <v>0.2186588921282799</v>
       </c>
       <c r="AJ3">
-        <v>-0.4167012879102617</v>
+        <v>-0.2553191489361702</v>
       </c>
       <c r="AK3">
-        <v>5.5414364640884</v>
+        <v>-0.9705882352941175</v>
       </c>
       <c r="AL3">
-        <v>0.446</v>
+        <v>0.762</v>
       </c>
       <c r="AM3">
-        <v>0.446</v>
+        <v>0.762</v>
       </c>
       <c r="AN3">
-        <v>0.4741935483870968</v>
+        <v>0.9036144578313252</v>
       </c>
       <c r="AO3">
-        <v>33.40807174887892</v>
+        <v>20.60367454068241</v>
       </c>
       <c r="AP3">
-        <v>-3.235483870967742</v>
+        <v>-1.590361445783132</v>
       </c>
       <c r="AQ3">
-        <v>33.40807174887892</v>
+        <v>20.60367454068241</v>
       </c>
     </row>
     <row r="4">
@@ -844,46 +835,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.508</v>
+        <v>0.547</v>
       </c>
       <c r="E4">
-        <v>0.477</v>
+        <v>0.608</v>
       </c>
       <c r="G4">
-        <v>0.421343146274149</v>
+        <v>0.2994764397905759</v>
       </c>
       <c r="H4">
-        <v>0.421343146274149</v>
+        <v>0.2994764397905759</v>
       </c>
       <c r="I4">
-        <v>0.3983440662373505</v>
+        <v>0.5267015706806283</v>
       </c>
       <c r="J4">
-        <v>0.3198684495016512</v>
+        <v>0.4168032621828434</v>
       </c>
       <c r="K4">
-        <v>31.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.2925482980680773</v>
+        <v>0.4</v>
       </c>
       <c r="M4">
-        <v>5.59</v>
+        <v>7.88</v>
       </c>
       <c r="N4">
-        <v>0.005943015096746757</v>
+        <v>0.008159884021952987</v>
       </c>
       <c r="O4">
-        <v>0.1757861635220126</v>
+        <v>0.1031413612565445</v>
       </c>
       <c r="P4">
-        <v>5.59</v>
+        <v>7.88</v>
       </c>
       <c r="Q4">
-        <v>0.005943015096746757</v>
+        <v>0.008159884021952987</v>
       </c>
       <c r="R4">
-        <v>0.1757861635220126</v>
+        <v>0.1031413612565445</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,73 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>153</v>
+        <v>181.3</v>
       </c>
       <c r="V4">
-        <v>0.1626621305549649</v>
+        <v>0.1877394636015326</v>
       </c>
       <c r="W4">
-        <v>0.2436781609195402</v>
+        <v>0.5338923829489868</v>
       </c>
       <c r="X4">
-        <v>0.07077599509938312</v>
+        <v>0.06026069111031268</v>
       </c>
       <c r="Y4">
-        <v>0.1729021658201571</v>
+        <v>0.4736316918386741</v>
       </c>
       <c r="Z4">
-        <v>5.009216589861754</v>
+        <v>382</v>
       </c>
       <c r="AA4">
-        <v>1.602290343817028</v>
+        <v>159.2188461538462</v>
       </c>
       <c r="AB4">
-        <v>0.07051325715048663</v>
+        <v>0.05998518550799921</v>
       </c>
       <c r="AC4">
-        <v>1.531777086666541</v>
+        <v>159.1588609683382</v>
       </c>
       <c r="AD4">
-        <v>10.4</v>
+        <v>15.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10.4</v>
+        <v>15.7</v>
       </c>
       <c r="AG4">
-        <v>-142.6</v>
+        <v>-165.6</v>
       </c>
       <c r="AH4">
-        <v>0.01093585699263933</v>
+        <v>0.01599755451395965</v>
       </c>
       <c r="AI4">
-        <v>0.06594800253646163</v>
+        <v>0.06808326105810927</v>
       </c>
       <c r="AJ4">
-        <v>-0.1786967418546366</v>
+        <v>-0.2069741282339708</v>
       </c>
       <c r="AK4">
-        <v>-30.34042553191478</v>
+        <v>-3.359026369168359</v>
       </c>
       <c r="AL4">
-        <v>0.637</v>
+        <v>0.632</v>
       </c>
       <c r="AM4">
-        <v>0.5570000000000001</v>
+        <v>-3.628</v>
       </c>
       <c r="AN4">
-        <v>0.235827664399093</v>
+        <v>0.1542239685658153</v>
       </c>
       <c r="AO4">
-        <v>67.97488226059654</v>
+        <v>159.1772151898734</v>
       </c>
       <c r="AP4">
-        <v>-3.233560090702948</v>
+        <v>-1.62671905697446</v>
       </c>
       <c r="AQ4">
-        <v>77.73788150807898</v>
+        <v>-27.72877618522602</v>
       </c>
     </row>
     <row r="5">
@@ -977,47 +968,41 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.188</v>
-      </c>
-      <c r="F5">
-        <v>0.03</v>
-      </c>
       <c r="G5">
-        <v>0.1733668341708542</v>
+        <v>0.1557496360989811</v>
       </c>
       <c r="H5">
-        <v>0.1733668341708542</v>
+        <v>0.1557496360989811</v>
       </c>
       <c r="I5">
-        <v>0.1641541038525963</v>
+        <v>0.1950509461426492</v>
       </c>
       <c r="J5">
-        <v>0.1294225513532575</v>
+        <v>0.1415427172391485</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>18.9</v>
       </c>
       <c r="L5">
-        <v>0.1256281407035176</v>
+        <v>0.1375545851528384</v>
       </c>
       <c r="M5">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="N5">
-        <v>0.02647329650092081</v>
+        <v>0.03212151394422311</v>
       </c>
       <c r="O5">
-        <v>0.7666666666666667</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="P5">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="Q5">
-        <v>0.02647329650092081</v>
+        <v>0.03212151394422311</v>
       </c>
       <c r="R5">
-        <v>0.7666666666666667</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,73 +1011,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>31.3</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>0.07205340699815839</v>
+        <v>0.04731075697211155</v>
       </c>
       <c r="W5">
-        <v>0.3211991434689507</v>
+        <v>0.3381037567084079</v>
       </c>
       <c r="X5">
-        <v>0.07141096375083038</v>
+        <v>0.06048523557423238</v>
       </c>
       <c r="Y5">
-        <v>0.2497881797181203</v>
+        <v>0.2776185211341755</v>
       </c>
       <c r="Z5">
-        <v>7.556962025316456</v>
+        <v>4.872340425531915</v>
       </c>
       <c r="AA5">
-        <v>0.9780413057961358</v>
+        <v>0.6896443031439363</v>
       </c>
       <c r="AB5">
-        <v>0.07030373335713712</v>
+        <v>0.05984235404378958</v>
       </c>
       <c r="AC5">
-        <v>0.9077375724389987</v>
+        <v>0.6298019491001468</v>
       </c>
       <c r="AD5">
-        <v>16.4</v>
+        <v>12.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16.4</v>
+        <v>12.2</v>
       </c>
       <c r="AG5">
-        <v>-14.9</v>
+        <v>-6.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.03637976929902396</v>
+        <v>0.02948284195263412</v>
       </c>
       <c r="AI5">
-        <v>0.2268326417704011</v>
+        <v>0.1296493092454835</v>
       </c>
       <c r="AJ5">
-        <v>-0.03551847437425507</v>
+        <v>-0.01722391084093212</v>
       </c>
       <c r="AK5">
-        <v>-0.3634146341463415</v>
+        <v>-0.09054593874833555</v>
       </c>
       <c r="AL5">
-        <v>0.621</v>
+        <v>1.09</v>
       </c>
       <c r="AM5">
-        <v>0.621</v>
+        <v>0.7260000000000001</v>
       </c>
       <c r="AN5">
-        <v>0.7922705314009661</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="AO5">
-        <v>31.56199677938809</v>
+        <v>24.58715596330275</v>
       </c>
       <c r="AP5">
-        <v>-0.7198067632850242</v>
+        <v>-0.2428571428571429</v>
       </c>
       <c r="AQ5">
-        <v>31.56199677938809</v>
+        <v>36.91460055096418</v>
       </c>
     </row>
     <row r="6">
@@ -1111,6 +1096,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.0512</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1118,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.02425093585306393</v>
+        <v>0.01267703774572122</v>
       </c>
       <c r="J6">
-        <v>0.02425093585306393</v>
+        <v>0.01267703774572122</v>
       </c>
       <c r="K6">
-        <v>1.01</v>
+        <v>-0.488</v>
       </c>
       <c r="L6">
-        <v>3.014925373134328</v>
+        <v>-0.7625</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1136,7 +1124,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1145,79 +1133,73 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.284</v>
+        <v>0.483</v>
       </c>
       <c r="V6">
-        <v>0.1154471544715447</v>
+        <v>0.2311004784688995</v>
       </c>
       <c r="W6">
-        <v>0.3126934984520124</v>
+        <v>-0.1229219143576826</v>
       </c>
       <c r="X6">
-        <v>0.07102911930179508</v>
+        <v>0.06033262898672344</v>
       </c>
       <c r="Y6">
-        <v>0.2416643791502173</v>
+        <v>-0.1832545433444061</v>
       </c>
       <c r="Z6">
-        <v>0.118989279523726</v>
+        <v>0.1711489196311564</v>
       </c>
       <c r="AA6">
-        <v>0.002885601384932172</v>
+        <v>0.002169661314303577</v>
       </c>
       <c r="AB6">
-        <v>0.07057401658769226</v>
+        <v>0.06002130861683216</v>
       </c>
       <c r="AC6">
-        <v>-0.06768841520276009</v>
+        <v>-0.05785164730252858</v>
       </c>
       <c r="AD6">
-        <v>0.044</v>
+        <v>0.034</v>
       </c>
       <c r="AE6">
-        <v>0.009379682446117919</v>
+        <v>0.009433479213692104</v>
       </c>
       <c r="AF6">
-        <v>0.05337968244611792</v>
+        <v>0.0434334792136921</v>
       </c>
       <c r="AG6">
-        <v>-0.2306203175538821</v>
+        <v>-0.4395665207863079</v>
       </c>
       <c r="AH6">
-        <v>0.02123820878275214</v>
+        <v>0.02035848768516567</v>
       </c>
       <c r="AI6">
-        <v>0.0132673738645676</v>
+        <v>0.01061052523126264</v>
       </c>
       <c r="AJ6">
-        <v>-0.103445958250073</v>
+        <v>-0.2663339821461501</v>
       </c>
       <c r="AK6">
-        <v>-0.0616734156834862</v>
+        <v>-0.1217489598733834</v>
       </c>
       <c r="AL6">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AP6">
-        <v>-23.06203175538821</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
+        <v>-43.95665207863079</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Numis Corporation Plc (AIM:NUM)</t>
+          <t>Walker Crips Group plc (LSE:WCW)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,10 +1219,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0105</v>
+        <v>0.00465</v>
       </c>
       <c r="E7">
-        <v>-0.147</v>
+        <v>0.0188</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1255,91 +1237,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>15.3</v>
+        <v>0.658</v>
       </c>
       <c r="L7">
-        <v>0.09763880025526485</v>
+        <v>0.01745358090185676</v>
       </c>
       <c r="M7">
-        <v>30.3</v>
+        <v>0.753</v>
       </c>
       <c r="N7">
-        <v>0.1212970376301041</v>
+        <v>0.05536764705882353</v>
       </c>
       <c r="O7">
-        <v>1.980392156862745</v>
+        <v>1.144376899696049</v>
       </c>
       <c r="P7">
-        <v>17.4</v>
+        <v>0.753</v>
       </c>
       <c r="Q7">
-        <v>0.06965572457966372</v>
+        <v>0.05536764705882353</v>
       </c>
       <c r="R7">
-        <v>1.137254901960784</v>
+        <v>1.144376899696049</v>
       </c>
       <c r="S7">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.4257425742574257</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>117.7</v>
+        <v>17.1</v>
       </c>
       <c r="V7">
-        <v>0.4711769415532426</v>
+        <v>1.257352941176471</v>
       </c>
       <c r="W7">
-        <v>0.06069020230067434</v>
+        <v>0.02492424242424243</v>
       </c>
       <c r="X7">
-        <v>0.07492147663012844</v>
+        <v>0.06398926716306773</v>
       </c>
       <c r="Y7">
-        <v>-0.0142312743294541</v>
+        <v>-0.0390650247388253</v>
       </c>
       <c r="Z7">
-        <v>1.25259792166267</v>
+        <v>3.381165919282513</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06961349734950266</v>
+        <v>0.05891550221890623</v>
       </c>
       <c r="AC7">
-        <v>-0.06961349734950266</v>
+        <v>-0.05891550221890623</v>
       </c>
       <c r="AD7">
-        <v>46.3</v>
+        <v>3.41</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>46.3</v>
+        <v>3.41</v>
       </c>
       <c r="AG7">
-        <v>-71.40000000000001</v>
+        <v>-13.69</v>
       </c>
       <c r="AH7">
-        <v>0.1563660925363053</v>
+        <v>0.2004703115814227</v>
       </c>
       <c r="AI7">
-        <v>0.1832212109220419</v>
+        <v>0.1163425452064142</v>
       </c>
       <c r="AJ7">
-        <v>-0.4002242152466368</v>
+        <v>152.1111111111084</v>
       </c>
       <c r="AK7">
-        <v>-0.528888888888889</v>
+        <v>-1.121212121212122</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.532</v>
+        <v>-0.308</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1353,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Walker Crips Group plc (LSE:WCW)</t>
+          <t>IG Group Holdings plc (LSE:IGG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1362,10 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0105</v>
+        <v>0.114</v>
       </c>
       <c r="E8">
-        <v>-0.238</v>
+        <v>0.1</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1380,91 +1362,91 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.274</v>
+        <v>452.1</v>
       </c>
       <c r="L8">
-        <v>0.007425474254742549</v>
+        <v>0.3602390438247012</v>
       </c>
       <c r="M8">
-        <v>0.202</v>
+        <v>468.1</v>
       </c>
       <c r="N8">
-        <v>0.01337748344370861</v>
+        <v>0.125096875918651</v>
       </c>
       <c r="O8">
-        <v>0.7372262773722628</v>
+        <v>1.035390400353904</v>
       </c>
       <c r="P8">
-        <v>0.202</v>
+        <v>233</v>
       </c>
       <c r="Q8">
-        <v>0.01337748344370861</v>
+        <v>0.06226783185012962</v>
       </c>
       <c r="R8">
-        <v>0.7372262773722628</v>
+        <v>0.515372705153727</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>235.1</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.5022431104464858</v>
       </c>
       <c r="U8">
-        <v>11.8</v>
+        <v>989.1</v>
       </c>
       <c r="V8">
-        <v>0.7814569536423842</v>
+        <v>0.264330954862503</v>
       </c>
       <c r="W8">
-        <v>0.009163879598662208</v>
+        <v>0.1769679414412652</v>
       </c>
       <c r="X8">
-        <v>0.0748131709057745</v>
+        <v>0.06167779057698004</v>
       </c>
       <c r="Y8">
-        <v>-0.06564929130711229</v>
+        <v>0.1152901508642851</v>
       </c>
       <c r="Z8">
-        <v>2.151603498542274</v>
+        <v>2.009285943003523</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06963221270784434</v>
+        <v>0.0594854292088831</v>
       </c>
       <c r="AC8">
-        <v>-0.06963221270784434</v>
+        <v>-0.0594854292088831</v>
       </c>
       <c r="AD8">
-        <v>2.73</v>
+        <v>394.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.73</v>
+        <v>394.3</v>
       </c>
       <c r="AG8">
-        <v>-9.07</v>
+        <v>-594.8</v>
       </c>
       <c r="AH8">
-        <v>0.1531127313516545</v>
+        <v>0.09532904598423675</v>
       </c>
       <c r="AI8">
-        <v>0.1013739324173784</v>
+        <v>0.1364501505346576</v>
       </c>
       <c r="AJ8">
-        <v>-1.504145936981758</v>
+        <v>-0.1889993962695815</v>
       </c>
       <c r="AK8">
-        <v>-0.5994712491738269</v>
+        <v>-0.3129538040618752</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.041</v>
+        <v>-37.4</v>
       </c>
       <c r="AQ8">
         <v>-0</v>
@@ -1478,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IG Group Holdings plc (LSE:IGG)</t>
+          <t>Cavendish Financial plc (AIM:CAV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,12 +1468,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.131</v>
-      </c>
-      <c r="E9">
-        <v>0.244</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1505,91 +1481,91 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>634.8</v>
+        <v>-4.49</v>
       </c>
       <c r="L9">
-        <v>0.5219965463366499</v>
+        <v>-0.1257703081232493</v>
       </c>
       <c r="M9">
-        <v>243.04</v>
+        <v>2.38</v>
       </c>
       <c r="N9">
-        <v>0.06207284057822955</v>
+        <v>0.04296028880866426</v>
       </c>
       <c r="O9">
-        <v>0.3828607435412729</v>
+        <v>-0.5300668151447661</v>
       </c>
       <c r="P9">
-        <v>234.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>0.05991724983398886</v>
+        <v>0.04296028880866426</v>
       </c>
       <c r="R9">
-        <v>0.3695652173913044</v>
+        <v>-0.5300668151447661</v>
       </c>
       <c r="S9">
-        <v>8.439999999999998</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.03472679394338379</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1570.3</v>
+        <v>15.1</v>
       </c>
       <c r="V9">
-        <v>0.4010573632323645</v>
+        <v>0.2725631768953068</v>
       </c>
       <c r="W9">
-        <v>0.3942612260108068</v>
+        <v>-0.1316715542521994</v>
       </c>
       <c r="X9">
-        <v>0.07295502940296564</v>
+        <v>0.06381970666089114</v>
       </c>
       <c r="Y9">
-        <v>0.3213061966078411</v>
+        <v>-0.1954912609130905</v>
       </c>
       <c r="Z9">
-        <v>1.737285714285714</v>
+        <v>1.022922636103152</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06997737658762625</v>
+        <v>0.0597966506600149</v>
       </c>
       <c r="AC9">
-        <v>-0.06997737658762625</v>
+        <v>-0.0597966506600149</v>
       </c>
       <c r="AD9">
-        <v>402</v>
+        <v>13.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>402</v>
+        <v>13.3</v>
       </c>
       <c r="AG9">
-        <v>-1168.3</v>
+        <v>-1.799999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.09311159494139992</v>
+        <v>0.1935953420669578</v>
       </c>
       <c r="AI9">
-        <v>0.1359623905029256</v>
+        <v>0.2166123778501629</v>
       </c>
       <c r="AJ9">
-        <v>-0.4252848458374285</v>
+        <v>-0.03358208955223878</v>
       </c>
       <c r="AK9">
-        <v>-0.8426860934795154</v>
+        <v>-0.03887688984881207</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-4.28</v>
+        <v>-0.142</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1603,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiske plc (AIM:FKE)</t>
+          <t>CMC Markets plc (LSE:CMCX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1611,8 +1587,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.0891</v>
+      </c>
+      <c r="E10">
+        <v>-0.208</v>
+      </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.003493589743589744</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1624,91 +1606,91 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-0.193</v>
+        <v>12.4</v>
       </c>
       <c r="L10">
-        <v>-0.03001555209953344</v>
+        <v>0.03974358974358975</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>29.39</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.07873024377176534</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.370161290322581</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>25.2</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.06750602732386819</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.032258064516129</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>4.190000000000001</v>
+      </c>
+      <c r="T10">
+        <v>0.142565498468867</v>
       </c>
       <c r="U10">
-        <v>4.79</v>
+        <v>215.8</v>
       </c>
       <c r="V10">
-        <v>0.4974039460020768</v>
+        <v>0.5780873292258237</v>
       </c>
       <c r="W10">
-        <v>-0.0187378640776699</v>
+        <v>0.02950975725844836</v>
       </c>
       <c r="X10">
-        <v>0.07152071563074222</v>
+        <v>0.06102450692270966</v>
       </c>
       <c r="Y10">
-        <v>-0.09025857970841213</v>
+        <v>-0.03151474966426131</v>
       </c>
       <c r="Z10">
-        <v>1.015156299336912</v>
+        <v>1.100141043723554</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07027919394934221</v>
+        <v>0.05993804038299948</v>
       </c>
       <c r="AC10">
-        <v>-0.07027919394934221</v>
+        <v>-0.05993804038299948</v>
       </c>
       <c r="AD10">
-        <v>0.408</v>
+        <v>24</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.408</v>
+        <v>24</v>
       </c>
       <c r="AG10">
-        <v>-4.382</v>
+        <v>-191.8</v>
       </c>
       <c r="AH10">
-        <v>0.04064554692169754</v>
+        <v>0.06040775232821545</v>
       </c>
       <c r="AI10">
-        <v>0.03882755995432052</v>
+        <v>0.05188067444876783</v>
       </c>
       <c r="AJ10">
-        <v>-0.8349847560975607</v>
+        <v>-1.056749311294766</v>
       </c>
       <c r="AK10">
-        <v>-0.7663518712836656</v>
+        <v>-0.7771474878444085</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.208</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1728,13 +1710,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.167</v>
+        <v>0.194</v>
       </c>
       <c r="E11">
-        <v>0.216</v>
+        <v>0.247</v>
       </c>
       <c r="G11">
-        <v>0.2003302146395157</v>
+        <v>0.1855203619909502</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1746,91 +1728,91 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>52.1</v>
+        <v>83.2</v>
       </c>
       <c r="L11">
-        <v>0.28673637864612</v>
+        <v>0.3137254901960785</v>
       </c>
       <c r="M11">
-        <v>33.3</v>
+        <v>43.33</v>
       </c>
       <c r="N11">
-        <v>0.01877325515841696</v>
+        <v>0.02643040136635354</v>
       </c>
       <c r="O11">
-        <v>0.6391554702495201</v>
+        <v>0.5207932692307692</v>
       </c>
       <c r="P11">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="Q11">
-        <v>0.01877325515841696</v>
+        <v>0.02476515798462852</v>
       </c>
       <c r="R11">
-        <v>0.6391554702495201</v>
+        <v>0.4879807692307692</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.729999999999997</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.06300484652665583</v>
       </c>
       <c r="U11">
-        <v>93.59999999999999</v>
+        <v>178.5</v>
       </c>
       <c r="V11">
-        <v>0.0527680685533882</v>
+        <v>0.1088812980358668</v>
       </c>
       <c r="W11">
-        <v>0.2951841359773371</v>
+        <v>0.559892328398385</v>
       </c>
       <c r="X11">
-        <v>0.07072219173372495</v>
+        <v>0.06014863314391796</v>
       </c>
       <c r="Y11">
-        <v>0.2244619442436122</v>
+        <v>0.499743695254467</v>
       </c>
       <c r="Z11">
-        <v>2.966046359777996</v>
+        <v>4.222257602292629</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07046286103539223</v>
+        <v>0.05995269661723338</v>
       </c>
       <c r="AC11">
-        <v>-0.07046286103539223</v>
+        <v>-0.05995269661723338</v>
       </c>
       <c r="AD11">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="AG11">
-        <v>-78</v>
+        <v>-163.4</v>
       </c>
       <c r="AH11">
-        <v>0.00871800603554264</v>
+        <v>0.009126624357812028</v>
       </c>
       <c r="AI11">
-        <v>0.09500609013398295</v>
+        <v>0.06936150666054203</v>
       </c>
       <c r="AJ11">
-        <v>-0.04599599009317137</v>
+        <v>-0.1107046070460705</v>
       </c>
       <c r="AK11">
-        <v>-1.104815864022663</v>
+        <v>-4.168367346938777</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.221</v>
+        <v>-2.92</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1853,13 +1835,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0621</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="E12">
-        <v>0.0765</v>
+        <v>0.0999</v>
       </c>
       <c r="G12">
-        <v>0.002251655629139073</v>
+        <v>0.001666666666666667</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1871,28 +1853,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>6.04</v>
+        <v>6.83</v>
       </c>
       <c r="L12">
-        <v>0.4</v>
+        <v>0.3925287356321839</v>
       </c>
       <c r="M12">
-        <v>7.08</v>
+        <v>6.82</v>
       </c>
       <c r="N12">
-        <v>0.08082191780821918</v>
+        <v>0.2029761904761905</v>
       </c>
       <c r="O12">
-        <v>1.172185430463576</v>
+        <v>0.9985358711566619</v>
       </c>
       <c r="P12">
-        <v>7.08</v>
+        <v>6.82</v>
       </c>
       <c r="Q12">
-        <v>0.08082191780821918</v>
+        <v>0.2029761904761905</v>
       </c>
       <c r="R12">
-        <v>1.172185430463576</v>
+        <v>0.9985358711566619</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1901,55 +1883,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>5.07</v>
+        <v>7.25</v>
       </c>
       <c r="V12">
-        <v>0.05787671232876713</v>
+        <v>0.2157738095238095</v>
       </c>
       <c r="W12">
-        <v>0.4541353383458646</v>
+        <v>1.128925619834711</v>
       </c>
       <c r="X12">
-        <v>0.0705203433509391</v>
+        <v>0.06020235836029486</v>
       </c>
       <c r="Y12">
-        <v>0.3836149949949255</v>
+        <v>1.068723261474416</v>
       </c>
       <c r="Z12">
-        <v>4.72761427676894</v>
+        <v>29.49152542372883</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07051301932705765</v>
+        <v>0.0600138571174122</v>
       </c>
       <c r="AC12">
-        <v>-0.07051301932705765</v>
+        <v>-0.0600138571174122</v>
       </c>
       <c r="AD12">
-        <v>0.027</v>
+        <v>0.423</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.027</v>
+        <v>0.423</v>
       </c>
       <c r="AG12">
-        <v>-5.043</v>
+        <v>-6.827</v>
       </c>
       <c r="AH12">
-        <v>0.0003081242082919648</v>
+        <v>0.01243276607001146</v>
       </c>
       <c r="AI12">
-        <v>0.004442981734408425</v>
+        <v>0.06254620730445069</v>
       </c>
       <c r="AJ12">
-        <v>-0.06108506849812858</v>
+        <v>-0.2549957046277966</v>
       </c>
       <c r="AK12">
-        <v>-5.007944389275076</v>
+        <v>14.01848049281314</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1966,7 +1948,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMC Markets plc (LSE:CMCX)</t>
+          <t>Hamilton Global Opportunities PLC (ENXTPA:ALHGO)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1974,110 +1956,107 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.119</v>
-      </c>
-      <c r="E13">
-        <v>0.081</v>
-      </c>
       <c r="G13">
-        <v>0.0005509964830011724</v>
+        <v>-1.683006535947712</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>-1.683006535947712</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-2.415032679738562</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>-2.415032679738562</v>
       </c>
       <c r="K13">
-        <v>81.40000000000001</v>
+        <v>-0.576</v>
       </c>
       <c r="L13">
-        <v>0.2385697538100821</v>
+        <v>-1.882352941176471</v>
       </c>
       <c r="M13">
-        <v>71.59999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.09503583753650119</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.8796068796068794</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>39.5</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.05242898858508097</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.4852579852579852</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>32.09999999999999</v>
-      </c>
-      <c r="T13">
-        <v>0.4483240223463686</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>157</v>
+        <v>1.37</v>
       </c>
       <c r="V13">
-        <v>0.208388638173613</v>
+        <v>0.0631336405529954</v>
       </c>
       <c r="W13">
-        <v>0.1651115618661258</v>
+        <v>-0.03789473684210526</v>
       </c>
       <c r="X13">
-        <v>0.07115703830163905</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="Y13">
-        <v>0.09395452356448672</v>
+        <v>-0.09789690508705164</v>
       </c>
       <c r="Z13">
-        <v>1.002055800293685</v>
+        <v>0.02628865979381444</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>-0.06348797250859108</v>
       </c>
       <c r="AB13">
-        <v>0.07051360238230464</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="AC13">
-        <v>-0.07051360238230464</v>
+        <v>-0.1234901407535375</v>
       </c>
       <c r="AD13">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>-136.6</v>
+        <v>-1.37</v>
       </c>
       <c r="AH13">
-        <v>0.02636340139570948</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.0463004993191103</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.2214656290531777</v>
+        <v>-0.06738809640924742</v>
       </c>
       <c r="AK13">
-        <v>-0.4816643159379407</v>
+        <v>-0.09834888729361092</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>-0</v>
+      </c>
+      <c r="AP13">
+        <v>1.858887381275441</v>
       </c>
     </row>
     <row r="14">
@@ -2088,7 +2067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cenkos Securities plc (AIM:CNKS)</t>
+          <t>Craven House Capital Plc (AIM:CRV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2096,455 +2075,71 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.114</v>
-      </c>
-      <c r="E14">
-        <v>-0.22</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14">
-        <v>1.83</v>
-      </c>
-      <c r="L14">
-        <v>0.04778067885117494</v>
+        <v>-5.52</v>
       </c>
       <c r="M14">
-        <v>7.78</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.3228215767634855</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>4.251366120218579</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.66</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.1103734439834025</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>1.453551912568306</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>5.12</v>
-      </c>
-      <c r="T14">
-        <v>0.6580976863753213</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.8008298755186721</v>
-      </c>
-      <c r="W14">
-        <v>0.05213675213675214</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>0.07656282880773614</v>
-      </c>
-      <c r="Y14">
-        <v>-0.024426076670984</v>
-      </c>
-      <c r="Z14">
-        <v>4.505882352941176</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="AB14">
-        <v>0.07051755013779436</v>
-      </c>
-      <c r="AC14">
-        <v>-0.07051755013779436</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="AD14">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>-13.17</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>0.2027786966589481</v>
-      </c>
-      <c r="AI14">
-        <v>0.1754938448325222</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-1.204940530649588</v>
-      </c>
-      <c r="AK14">
-        <v>-0.8426103646833015</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AM14">
-        <v>-0.068</v>
+        <v>0.065</v>
+      </c>
+      <c r="AO14">
+        <v>-2.861538461538462</v>
       </c>
       <c r="AQ14">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>finnCap Group plc (AIM:FCAP)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>-1.52</v>
-      </c>
-      <c r="L15">
-        <v>-0.03725490196078432</v>
-      </c>
-      <c r="M15">
-        <v>2.059</v>
-      </c>
-      <c r="N15">
-        <v>0.0830241935483871</v>
-      </c>
-      <c r="O15">
-        <v>-1.354605263157895</v>
-      </c>
-      <c r="P15">
-        <v>1.12</v>
-      </c>
-      <c r="Q15">
-        <v>0.04516129032258065</v>
-      </c>
-      <c r="R15">
-        <v>-0.736842105263158</v>
-      </c>
-      <c r="S15">
-        <v>0.9390000000000001</v>
-      </c>
-      <c r="T15">
-        <v>0.4560466245750364</v>
-      </c>
-      <c r="U15">
-        <v>12.4</v>
-      </c>
-      <c r="V15">
-        <v>0.5</v>
-      </c>
-      <c r="W15">
-        <v>-0.03438914027149321</v>
-      </c>
-      <c r="X15">
-        <v>0.08317264239473134</v>
-      </c>
-      <c r="Y15">
-        <v>-0.1175617826662246</v>
-      </c>
-      <c r="Z15">
-        <v>1.189504373177842</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.07052078571256343</v>
-      </c>
-      <c r="AC15">
-        <v>-0.07052078571256343</v>
-      </c>
-      <c r="AD15">
-        <v>13.2</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>13.2</v>
-      </c>
-      <c r="AG15">
-        <v>0.7999999999999989</v>
-      </c>
-      <c r="AH15">
-        <v>0.3473684210526315</v>
-      </c>
-      <c r="AI15">
-        <v>0.2790697674418605</v>
-      </c>
-      <c r="AJ15">
-        <v>0.03124999999999996</v>
-      </c>
-      <c r="AK15">
-        <v>0.02292263610315183</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-0.031</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Craven House Capital Plc (AIM:CRV)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="K16">
-        <v>-0.236</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0.001</v>
-      </c>
-      <c r="V16">
-        <v>0.003048780487804878</v>
-      </c>
-      <c r="W16">
-        <v>-0.04394785847299813</v>
-      </c>
-      <c r="X16">
-        <v>0.07051301243196936</v>
-      </c>
-      <c r="Y16">
-        <v>-0.1144608709049675</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>-0.02832861189801699</v>
-      </c>
-      <c r="AB16">
-        <v>0.07051301243196936</v>
-      </c>
-      <c r="AC16">
-        <v>-0.09884162432998636</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>-0.001</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.003058103975535168</v>
-      </c>
-      <c r="AK16">
-        <v>-0.000194969779684149</v>
-      </c>
-      <c r="AL16">
-        <v>0.056</v>
-      </c>
-      <c r="AM16">
-        <v>0.056</v>
-      </c>
-      <c r="AO16">
-        <v>-3.214285714285714</v>
-      </c>
-      <c r="AQ16">
-        <v>-3.214285714285714</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hamilton Global Opportunities PLC (ENXTPA:ALHGO)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>-1.37037037037037</v>
-      </c>
-      <c r="H17">
-        <v>-1.37037037037037</v>
-      </c>
-      <c r="I17">
-        <v>-0.3518518518518519</v>
-      </c>
-      <c r="J17">
-        <v>-0.2687268518518519</v>
-      </c>
-      <c r="K17">
-        <v>1.83</v>
-      </c>
-      <c r="L17">
-        <v>8.472222222222223</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>-0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>-0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>3.56</v>
-      </c>
-      <c r="V17">
-        <v>0.1663551401869159</v>
-      </c>
-      <c r="W17">
-        <v>0.1694444444444445</v>
-      </c>
-      <c r="X17">
-        <v>0.07051301243196936</v>
-      </c>
-      <c r="Y17">
-        <v>0.09893143201247509</v>
-      </c>
-      <c r="Z17">
-        <v>1.079999999999994</v>
-      </c>
-      <c r="AA17">
-        <v>-0.2902249999999985</v>
-      </c>
-      <c r="AB17">
-        <v>0.07051301243196936</v>
-      </c>
-      <c r="AC17">
-        <v>-0.3607380124319678</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>-3.56</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>-0.1995515695067265</v>
-      </c>
-      <c r="AK17">
-        <v>-0.3058419243986255</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>-0</v>
-      </c>
-      <c r="AP17">
-        <v>48.10810810810811</v>
+        <v>-2.861538461538462</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,113 +587,125 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.167</v>
+      </c>
+      <c r="E2">
+        <v>0.2485</v>
+      </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.06241897726730272</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.04576982945095018</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.04705724982896607</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.03852119265941337</v>
       </c>
       <c r="K2">
-        <v>186.6</v>
+        <v>953.085</v>
       </c>
       <c r="L2">
-        <v>0.121208184475479</v>
+        <v>0.2230225305207076</v>
       </c>
       <c r="M2">
-        <v>40.3312</v>
+        <v>762.2471999999999</v>
       </c>
       <c r="N2">
-        <v>0.01777801287137442</v>
+        <v>0.06526156090644766</v>
       </c>
       <c r="O2">
-        <v>0.2161371918542337</v>
+        <v>0.7997683312611151</v>
       </c>
       <c r="P2">
-        <v>40.3312</v>
+        <v>393.3802</v>
       </c>
       <c r="Q2">
-        <v>0.01777801287137442</v>
+        <v>0.0336801576728528</v>
       </c>
       <c r="R2">
-        <v>0.2161371918542337</v>
+        <v>0.4127440889322568</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>368.867</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.4839204394584854</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2125.291</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.1819617153600893</v>
       </c>
       <c r="W2">
-        <v>0.2404949091377755</v>
+        <v>0.1279681471049589</v>
       </c>
       <c r="X2">
-        <v>0.09763626233108397</v>
+        <v>0.06658131295533715</v>
       </c>
       <c r="Y2">
-        <v>0.1428586468066915</v>
+        <v>0.06138683414962171</v>
       </c>
       <c r="Z2">
-        <v>0.3044114448421095</v>
+        <v>0.6392768070453448</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06467145237759697</v>
+        <v>0.06542362477966333</v>
       </c>
       <c r="AC2">
-        <v>-0.06467145237759697</v>
+        <v>-0.06459300005623717</v>
       </c>
       <c r="AD2">
-        <v>4865.9</v>
+        <v>5439.513999999999</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.0960965695605797</v>
       </c>
       <c r="AF2">
-        <v>4865.9</v>
+        <v>5439.61009656956</v>
       </c>
       <c r="AG2">
-        <v>4865.9</v>
+        <v>3314.31909656956</v>
       </c>
       <c r="AH2">
-        <v>0.6820239680426098</v>
+        <v>0.3177436983160825</v>
       </c>
       <c r="AI2">
-        <v>0.8465084722173898</v>
+        <v>0.5373351250410532</v>
       </c>
       <c r="AJ2">
-        <v>0.6820239680426098</v>
+        <v>0.22104008858518</v>
       </c>
       <c r="AK2">
-        <v>0.8465084722173898</v>
+        <v>0.4143924960108071</v>
       </c>
       <c r="AL2">
-        <v>107.4</v>
+        <v>110.83</v>
       </c>
       <c r="AM2">
-        <v>53.7</v>
+        <v>-37.952</v>
+      </c>
+      <c r="AN2">
+        <v>26.09017262301608</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>1.81373274384192</v>
+      </c>
+      <c r="AP2">
+        <v>15.89685353457286</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>-5.296585160202361</v>
       </c>
     </row>
     <row r="3">
@@ -704,121 +716,1511 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Alpha Group International plc (LSE:ALPH)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.473</v>
+      </c>
+      <c r="E3">
+        <v>0.57</v>
+      </c>
+      <c r="G3">
+        <v>0.5654715510522212</v>
+      </c>
+      <c r="H3">
+        <v>0.5654715510522212</v>
+      </c>
+      <c r="I3">
+        <v>0.5931410756040529</v>
+      </c>
+      <c r="J3">
+        <v>0.4442009190801331</v>
+      </c>
+      <c r="K3">
+        <v>118.9</v>
+      </c>
+      <c r="L3">
+        <v>0.4633671083398285</v>
+      </c>
+      <c r="M3">
+        <v>33.83</v>
+      </c>
+      <c r="N3">
+        <v>0.02742157736889033</v>
+      </c>
+      <c r="O3">
+        <v>0.284524810765349</v>
+      </c>
+      <c r="P3">
+        <v>8.73</v>
+      </c>
+      <c r="Q3">
+        <v>0.007076274621058604</v>
+      </c>
+      <c r="R3">
+        <v>0.07342304457527334</v>
+      </c>
+      <c r="S3">
+        <v>25.1</v>
+      </c>
+      <c r="T3">
+        <v>0.7419450192137156</v>
+      </c>
+      <c r="U3">
+        <v>240.2</v>
+      </c>
+      <c r="V3">
+        <v>0.1946988733079354</v>
+      </c>
+      <c r="W3">
+        <v>0.5699904122722915</v>
+      </c>
+      <c r="X3">
+        <v>0.06599353994128637</v>
+      </c>
+      <c r="Y3">
+        <v>0.5039968723310051</v>
+      </c>
+      <c r="Z3">
+        <v>5.96744186046512</v>
+      </c>
+      <c r="AA3">
+        <v>2.650743158975866</v>
+      </c>
+      <c r="AB3">
+        <v>0.06555600653681397</v>
+      </c>
+      <c r="AC3">
+        <v>2.585187152439052</v>
+      </c>
+      <c r="AD3">
+        <v>27.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>27.5</v>
+      </c>
+      <c r="AG3">
+        <v>-212.7</v>
+      </c>
+      <c r="AH3">
+        <v>0.0218046305106248</v>
+      </c>
+      <c r="AI3">
+        <v>0.08466748768472906</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.2083251714005876</v>
+      </c>
+      <c r="AK3">
+        <v>-2.51418439716312</v>
+      </c>
+      <c r="AL3">
+        <v>1.39</v>
+      </c>
+      <c r="AM3">
+        <v>-6.03</v>
+      </c>
+      <c r="AN3">
+        <v>0.1753826530612245</v>
+      </c>
+      <c r="AO3">
+        <v>109.4964028776978</v>
+      </c>
+      <c r="AP3">
+        <v>-1.356505102040816</v>
+      </c>
+      <c r="AQ3">
+        <v>-25.24046434494196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FRP Advisory Group plc (AIM:FRP)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.198</v>
+      </c>
+      <c r="G4">
+        <v>0.2086634970945589</v>
+      </c>
+      <c r="H4">
+        <v>0.2086634970945589</v>
+      </c>
+      <c r="I4">
+        <v>0.2509244585314316</v>
+      </c>
+      <c r="J4">
+        <v>0.1825394666140672</v>
+      </c>
+      <c r="K4">
+        <v>33.9</v>
+      </c>
+      <c r="L4">
+        <v>0.179080824088748</v>
+      </c>
+      <c r="M4">
+        <v>15.4</v>
+      </c>
+      <c r="N4">
+        <v>0.03401811354097636</v>
+      </c>
+      <c r="O4">
+        <v>0.4542772861356932</v>
+      </c>
+      <c r="P4">
+        <v>15.4</v>
+      </c>
+      <c r="Q4">
+        <v>0.03401811354097636</v>
+      </c>
+      <c r="R4">
+        <v>0.4542772861356932</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>28.6</v>
+      </c>
+      <c r="V4">
+        <v>0.06317649657609897</v>
+      </c>
+      <c r="W4">
+        <v>0.4139194139194139</v>
+      </c>
+      <c r="X4">
+        <v>0.06637224474494291</v>
+      </c>
+      <c r="Y4">
+        <v>0.347547169174471</v>
+      </c>
+      <c r="Z4">
+        <v>3.170854271356784</v>
+      </c>
+      <c r="AA4">
+        <v>0.5788060474044039</v>
+      </c>
+      <c r="AB4">
+        <v>0.0655265620619201</v>
+      </c>
+      <c r="AC4">
+        <v>0.5132794853424838</v>
+      </c>
+      <c r="AD4">
+        <v>21.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>21.6</v>
+      </c>
+      <c r="AG4">
+        <v>-7</v>
+      </c>
+      <c r="AH4">
+        <v>0.04554079696394687</v>
+      </c>
+      <c r="AI4">
+        <v>0.1637604245640637</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.01570563159075612</v>
+      </c>
+      <c r="AK4">
+        <v>-0.06776379477250727</v>
+      </c>
+      <c r="AL4">
+        <v>1.03</v>
+      </c>
+      <c r="AM4">
+        <v>0.901</v>
+      </c>
+      <c r="AN4">
+        <v>0.4408163265306123</v>
+      </c>
+      <c r="AO4">
+        <v>46.11650485436893</v>
+      </c>
+      <c r="AP4">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="AQ4">
+        <v>52.71920088790233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Argentex Group PLC (AIM:AGFX)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.2408427876823339</v>
+      </c>
+      <c r="H5">
+        <v>0.1896272285251215</v>
+      </c>
+      <c r="I5">
+        <v>0.03273905996758509</v>
+      </c>
+      <c r="J5">
+        <v>0.01636952998379254</v>
+      </c>
+      <c r="K5">
+        <v>0.253</v>
+      </c>
+      <c r="L5">
+        <v>0.004100486223662885</v>
+      </c>
+      <c r="M5">
+        <v>4.3</v>
+      </c>
+      <c r="N5">
+        <v>0.09907834101382489</v>
+      </c>
+      <c r="O5">
+        <v>16.99604743083004</v>
+      </c>
+      <c r="P5">
+        <v>4.3</v>
+      </c>
+      <c r="Q5">
+        <v>0.09907834101382489</v>
+      </c>
+      <c r="R5">
+        <v>16.99604743083004</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>60.9</v>
+      </c>
+      <c r="V5">
+        <v>1.403225806451613</v>
+      </c>
+      <c r="W5">
+        <v>0.004720149253731343</v>
+      </c>
+      <c r="X5">
+        <v>0.07053534162933187</v>
+      </c>
+      <c r="Y5">
+        <v>-0.06581519237560052</v>
+      </c>
+      <c r="Z5">
+        <v>2.268382352941177</v>
+      </c>
+      <c r="AA5">
+        <v>0.03713235294117648</v>
+      </c>
+      <c r="AB5">
+        <v>0.06446881587098943</v>
+      </c>
+      <c r="AC5">
+        <v>-0.02733646292981295</v>
+      </c>
+      <c r="AD5">
+        <v>14.2</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>14.2</v>
+      </c>
+      <c r="AG5">
+        <v>-46.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.2465277777777778</v>
+      </c>
+      <c r="AI5">
+        <v>0.2094395280235988</v>
+      </c>
+      <c r="AJ5">
+        <v>14.15151515151513</v>
+      </c>
+      <c r="AK5">
+        <v>-6.768115942028987</v>
+      </c>
+      <c r="AL5">
+        <v>1.01</v>
+      </c>
+      <c r="AM5">
+        <v>1.01</v>
+      </c>
+      <c r="AN5">
+        <v>4.316109422492401</v>
+      </c>
+      <c r="AO5">
+        <v>2</v>
+      </c>
+      <c r="AP5">
+        <v>-14.19452887537994</v>
+      </c>
+      <c r="AQ5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fiske plc (AIM:FKE)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.008158804044946353</v>
+      </c>
+      <c r="J6">
+        <v>0.00710981495345325</v>
+      </c>
+      <c r="K6">
+        <v>1.04</v>
+      </c>
+      <c r="L6">
+        <v>0.1112299465240642</v>
+      </c>
+      <c r="M6">
+        <v>0.038</v>
+      </c>
+      <c r="N6">
+        <v>0.003653846153846154</v>
+      </c>
+      <c r="O6">
+        <v>0.03653846153846153</v>
+      </c>
+      <c r="P6">
+        <v>0.038</v>
+      </c>
+      <c r="Q6">
+        <v>0.003653846153846154</v>
+      </c>
+      <c r="R6">
+        <v>0.03653846153846153</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>6.26</v>
+      </c>
+      <c r="V6">
+        <v>0.6019230769230769</v>
+      </c>
+      <c r="W6">
+        <v>0.09904761904761905</v>
+      </c>
+      <c r="X6">
+        <v>0.06591870546375513</v>
+      </c>
+      <c r="Y6">
+        <v>0.03312891358386393</v>
+      </c>
+      <c r="Z6">
+        <v>1.477892643932843</v>
+      </c>
+      <c r="AA6">
+        <v>0.01050754321943229</v>
+      </c>
+      <c r="AB6">
+        <v>0.06557937752698281</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05507183430755053</v>
+      </c>
+      <c r="AD6">
+        <v>0.091</v>
+      </c>
+      <c r="AE6">
+        <v>0.08857591089875799</v>
+      </c>
+      <c r="AF6">
+        <v>0.179575910898758</v>
+      </c>
+      <c r="AG6">
+        <v>-6.080424089101242</v>
+      </c>
+      <c r="AH6">
+        <v>0.01697382885771105</v>
+      </c>
+      <c r="AI6">
+        <v>0.01427519593432209</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.407643762842475</v>
+      </c>
+      <c r="AK6">
+        <v>-0.962156982498608</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.518</v>
+      </c>
+      <c r="AN6">
+        <v>0.9680851063829787</v>
+      </c>
+      <c r="AP6">
+        <v>-64.6853626500132</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Marechale Capital Plc (AIM:MAC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0196</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.01018161170475809</v>
+      </c>
+      <c r="J7">
+        <v>0.01018161170475809</v>
+      </c>
+      <c r="K7">
+        <v>-0.264</v>
+      </c>
+      <c r="L7">
+        <v>-0.4137931034482759</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.288</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>-0.06518518518518519</v>
+      </c>
+      <c r="X7">
+        <v>0.06589828678205323</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1310834719672384</v>
+      </c>
+      <c r="Z7">
+        <v>0.176803754322026</v>
+      </c>
+      <c r="AA7">
+        <v>0.001800147174450313</v>
+      </c>
+      <c r="AB7">
+        <v>0.0656151334230981</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06381498624864779</v>
+      </c>
+      <c r="AD7">
+        <v>0.023</v>
+      </c>
+      <c r="AE7">
+        <v>0.007520658661821703</v>
+      </c>
+      <c r="AF7">
+        <v>0.0305206586618217</v>
+      </c>
+      <c r="AG7">
+        <v>-0.2574793413381783</v>
+      </c>
+      <c r="AH7">
+        <v>0.01564744189008527</v>
+      </c>
+      <c r="AI7">
+        <v>0.007389058470829578</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.1548728672914211</v>
+      </c>
+      <c r="AK7">
+        <v>-0.06700792636150638</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>2.875</v>
+      </c>
+      <c r="AP7">
+        <v>-32.18491766727229</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cavendish Financial plc (AIM:CAV)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.142</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-3.04</v>
+      </c>
+      <c r="L8">
+        <v>-0.03671497584541063</v>
+      </c>
+      <c r="M8">
+        <v>2.996</v>
+      </c>
+      <c r="N8">
+        <v>0.06320675105485232</v>
+      </c>
+      <c r="O8">
+        <v>-0.9855263157894737</v>
+      </c>
+      <c r="P8">
+        <v>2.996</v>
+      </c>
+      <c r="Q8">
+        <v>0.06320675105485232</v>
+      </c>
+      <c r="R8">
+        <v>-0.9855263157894737</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>23.1</v>
+      </c>
+      <c r="V8">
+        <v>0.4873417721518988</v>
+      </c>
+      <c r="W8">
+        <v>-0.06320166320166321</v>
+      </c>
+      <c r="X8">
+        <v>0.07024975225654623</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1334514154582094</v>
+      </c>
+      <c r="Z8">
+        <v>1.788336933045356</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06452224531314579</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06452224531314579</v>
+      </c>
+      <c r="AD8">
+        <v>14.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>14.6</v>
+      </c>
+      <c r="AG8">
+        <v>-8.500000000000002</v>
+      </c>
+      <c r="AH8">
+        <v>0.2354838709677419</v>
+      </c>
+      <c r="AI8">
+        <v>0.2150220913107511</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.218508997429306</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1897321428571429</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.836</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Marex Group plc (NasdaqGS:MRX)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F9">
         <v>0.1</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>186.6</v>
       </c>
-      <c r="L3">
+      <c r="L9">
         <v>0.121208184475479</v>
       </c>
-      <c r="M3">
+      <c r="M9">
         <v>40.3312</v>
       </c>
-      <c r="N3">
+      <c r="N9">
         <v>0.01777801287137442</v>
       </c>
-      <c r="O3">
+      <c r="O9">
         <v>0.2161371918542337</v>
       </c>
-      <c r="P3">
+      <c r="P9">
         <v>40.3312</v>
       </c>
-      <c r="Q3">
+      <c r="Q9">
         <v>0.01777801287137442</v>
       </c>
-      <c r="R3">
+      <c r="R9">
         <v>0.2161371918542337</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
         <v>0.2404949091377755</v>
       </c>
-      <c r="X3">
-        <v>0.09763626233108397</v>
-      </c>
-      <c r="Y3">
-        <v>0.1428586468066915</v>
-      </c>
-      <c r="Z3">
+      <c r="X9">
+        <v>0.09761205428552455</v>
+      </c>
+      <c r="Y9">
+        <v>0.1428828548522509</v>
+      </c>
+      <c r="Z9">
         <v>0.3044114448421095</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06467145237759697</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06467145237759697</v>
-      </c>
-      <c r="AD3">
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06466375479932854</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06466375479932854</v>
+      </c>
+      <c r="AD9">
         <v>4865.9</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>4865.9</v>
       </c>
-      <c r="AG3">
+      <c r="AG9">
         <v>4865.9</v>
       </c>
-      <c r="AH3">
+      <c r="AH9">
         <v>0.6820239680426098</v>
       </c>
-      <c r="AI3">
+      <c r="AI9">
         <v>0.8465084722173898</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ9">
         <v>0.6820239680426098</v>
       </c>
-      <c r="AK3">
+      <c r="AK9">
         <v>0.8465084722173898</v>
       </c>
-      <c r="AL3">
+      <c r="AL9">
         <v>107.4</v>
       </c>
-      <c r="AM3">
+      <c r="AM9">
         <v>53.7</v>
       </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Walker Crips Group plc (LSE:WCW)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.00621</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-1.24</v>
+      </c>
+      <c r="L10">
+        <v>-0.02903981264637002</v>
+      </c>
+      <c r="M10">
+        <v>0.285</v>
+      </c>
+      <c r="N10">
+        <v>0.0314569536423841</v>
+      </c>
+      <c r="O10">
+        <v>-0.2298387096774193</v>
+      </c>
+      <c r="P10">
+        <v>0.285</v>
+      </c>
+      <c r="Q10">
+        <v>0.0314569536423841</v>
+      </c>
+      <c r="R10">
+        <v>-0.2298387096774193</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>17.1</v>
+      </c>
+      <c r="V10">
+        <v>1.887417218543046</v>
+      </c>
+      <c r="W10">
+        <v>-0.04787644787644788</v>
+      </c>
+      <c r="X10">
+        <v>0.07026515328198915</v>
+      </c>
+      <c r="Y10">
+        <v>-0.118141601158437</v>
+      </c>
+      <c r="Z10">
+        <v>6.22448979591837</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06496198850979286</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06496198850979286</v>
+      </c>
+      <c r="AD10">
+        <v>2.8</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>2.8</v>
+      </c>
+      <c r="AG10">
+        <v>-14.3</v>
+      </c>
+      <c r="AH10">
+        <v>0.2360876897133221</v>
+      </c>
+      <c r="AI10">
+        <v>0.09395973154362415</v>
+      </c>
+      <c r="AJ10">
+        <v>2.729007633587786</v>
+      </c>
+      <c r="AK10">
+        <v>-1.125984251968504</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-0.717</v>
+      </c>
+      <c r="AQ10">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IG Group Holdings plc (LSE:IGG)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.143</v>
+      </c>
+      <c r="E11">
+        <v>0.142</v>
+      </c>
+      <c r="F11">
+        <v>0.0653</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>391.5</v>
+      </c>
+      <c r="L11">
+        <v>0.322354878550844</v>
+      </c>
+      <c r="M11">
+        <v>556.3</v>
+      </c>
+      <c r="N11">
+        <v>0.12665057827156</v>
+      </c>
+      <c r="O11">
+        <v>1.420945083014048</v>
+      </c>
+      <c r="P11">
+        <v>226.9</v>
+      </c>
+      <c r="Q11">
+        <v>0.0516574082506147</v>
+      </c>
+      <c r="R11">
+        <v>0.5795657726692209</v>
+      </c>
+      <c r="S11">
+        <v>329.4</v>
+      </c>
+      <c r="T11">
+        <v>0.5921265504224339</v>
+      </c>
+      <c r="U11">
+        <v>1251</v>
+      </c>
+      <c r="V11">
+        <v>0.2848101265822785</v>
+      </c>
+      <c r="W11">
+        <v>0.1568886751622986</v>
+      </c>
+      <c r="X11">
+        <v>0.06705058824598484</v>
+      </c>
+      <c r="Y11">
+        <v>0.08983808691631379</v>
+      </c>
+      <c r="Z11">
+        <v>1.061811505507956</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06502492554152317</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06502492554152317</v>
+      </c>
+      <c r="AD11">
+        <v>409.6</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>409.6</v>
+      </c>
+      <c r="AG11">
+        <v>-841.4</v>
+      </c>
+      <c r="AH11">
+        <v>0.08529779258642232</v>
+      </c>
+      <c r="AI11">
+        <v>0.1455682706660033</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.2369473387778091</v>
+      </c>
+      <c r="AK11">
+        <v>-0.5383926286153059</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-76.2</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CMC Markets Plc (LSE:CMCX)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.191</v>
+      </c>
+      <c r="E12">
+        <v>0.27</v>
+      </c>
+      <c r="F12">
+        <v>0.138</v>
+      </c>
+      <c r="G12">
+        <v>0.00230530802014723</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>113.3</v>
+      </c>
+      <c r="L12">
+        <v>0.2194885703215808</v>
+      </c>
+      <c r="M12">
+        <v>45.1</v>
+      </c>
+      <c r="N12">
+        <v>0.05218095568668287</v>
+      </c>
+      <c r="O12">
+        <v>0.3980582524271845</v>
+      </c>
+      <c r="P12">
+        <v>30.8</v>
+      </c>
+      <c r="Q12">
+        <v>0.03563577461529562</v>
+      </c>
+      <c r="R12">
+        <v>0.2718446601941747</v>
+      </c>
+      <c r="S12">
+        <v>14.3</v>
+      </c>
+      <c r="T12">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="U12">
+        <v>233.3</v>
+      </c>
+      <c r="V12">
+        <v>0.269929422654171</v>
+      </c>
+      <c r="W12">
+        <v>0.2583219334245326</v>
+      </c>
+      <c r="X12">
+        <v>0.06679038116573138</v>
+      </c>
+      <c r="Y12">
+        <v>0.1915315522588012</v>
+      </c>
+      <c r="Z12">
+        <v>2.091572123176662</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06532068749740656</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06532068749740656</v>
+      </c>
+      <c r="AD12">
+        <v>65.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>65.5</v>
+      </c>
+      <c r="AG12">
+        <v>-167.8</v>
+      </c>
+      <c r="AH12">
+        <v>0.07044525704452571</v>
+      </c>
+      <c r="AI12">
+        <v>0.1062794093785494</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.24091888011486</v>
+      </c>
+      <c r="AK12">
+        <v>-0.4381201044386424</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AJ Bell plc (LSE:AJB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.207</v>
+      </c>
+      <c r="E13">
+        <v>0.227</v>
+      </c>
+      <c r="F13">
+        <v>0.141</v>
+      </c>
+      <c r="G13">
+        <v>0.1856071130869686</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>113</v>
+      </c>
+      <c r="L13">
+        <v>0.3139761044734649</v>
+      </c>
+      <c r="M13">
+        <v>63.6</v>
+      </c>
+      <c r="N13">
+        <v>0.02722602739726027</v>
+      </c>
+      <c r="O13">
+        <v>0.5628318584070796</v>
+      </c>
+      <c r="P13">
+        <v>63.6</v>
+      </c>
+      <c r="Q13">
+        <v>0.02722602739726027</v>
+      </c>
+      <c r="R13">
+        <v>0.5628318584070796</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>263.6</v>
+      </c>
+      <c r="V13">
+        <v>0.1128424657534247</v>
+      </c>
+      <c r="W13">
+        <v>0.5577492596248766</v>
+      </c>
+      <c r="X13">
+        <v>0.06577436413559229</v>
+      </c>
+      <c r="Y13">
+        <v>0.4919748954892844</v>
+      </c>
+      <c r="Z13">
+        <v>11.73459406586241</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.0656251139511997</v>
+      </c>
+      <c r="AC13">
+        <v>-0.0656251139511997</v>
+      </c>
+      <c r="AD13">
+        <v>17.7</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>17.7</v>
+      </c>
+      <c r="AG13">
+        <v>-245.9</v>
+      </c>
+      <c r="AH13">
+        <v>0.007520074775884777</v>
+      </c>
+      <c r="AI13">
+        <v>0.06080384747509447</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.1176498732118081</v>
+      </c>
+      <c r="AK13">
+        <v>-8.941818181818201</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-9.26</v>
+      </c>
+      <c r="AQ13">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hamilton Global Opportunities PLC (ENXTPA:ALHGO)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>-2.3125</v>
+      </c>
+      <c r="H14">
+        <v>-2.3125</v>
+      </c>
+      <c r="I14">
+        <v>-2.315789473684211</v>
+      </c>
+      <c r="J14">
+        <v>-2.315789473684211</v>
+      </c>
+      <c r="K14">
+        <v>-0.864</v>
+      </c>
+      <c r="L14">
+        <v>-2.842105263157895</v>
+      </c>
+      <c r="M14">
+        <v>0.067</v>
+      </c>
+      <c r="N14">
+        <v>0.00335</v>
+      </c>
+      <c r="O14">
+        <v>-0.07754629629629631</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0.067</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="V14">
+        <v>0.04715</v>
+      </c>
+      <c r="W14">
+        <v>-0.0561038961038961</v>
+      </c>
+      <c r="X14">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1217653915102421</v>
+      </c>
+      <c r="Z14">
+        <v>0.02282282282282282</v>
+      </c>
+      <c r="AA14">
+        <v>-0.05285285285285285</v>
+      </c>
+      <c r="AB14">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1185143482591989</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-0.9429999999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.04948312955869234</v>
+      </c>
+      <c r="AK14">
+        <v>-0.06708401508145408</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-0.002</v>
+      </c>
+      <c r="AN14">
+        <v>-0</v>
+      </c>
+      <c r="AP14">
+        <v>1.341394025604552</v>
+      </c>
+      <c r="AQ14">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
